--- a/api/clv3/xlsx/en/AreaCodeM49.xlsx
+++ b/api/clv3/xlsx/en/AreaCodeM49.xlsx
@@ -43,33 +43,33 @@
     <t>iso-alpha-3-code</t>
   </si>
   <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
     <t>intermediate-region-code</t>
   </si>
   <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
+    <t>global-code</t>
+  </si>
+  <si>
     <t>intermediate-region-name</t>
   </si>
   <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>region-name</t>
+  </si>
+  <si>
     <t>global-name</t>
   </si>
   <si>
-    <t>region-name</t>
-  </si>
-  <si>
-    <t>region-code</t>
-  </si>
-  <si>
-    <t>sub-region-code</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>global-code</t>
-  </si>
-  <si>
     <t>012</t>
   </si>
   <si>
@@ -82,27 +82,27 @@
     <t>DZA</t>
   </si>
   <si>
+    <t>Northern Africa</t>
+  </si>
+  <si>
+    <t>015</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>DZ</t>
+  </si>
+  <si>
+    <t>Africa</t>
+  </si>
+  <si>
     <t>World</t>
   </si>
   <si>
-    <t>Africa</t>
-  </si>
-  <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t>015</t>
-  </si>
-  <si>
-    <t>Northern Africa</t>
-  </si>
-  <si>
-    <t>DZ</t>
-  </si>
-  <si>
-    <t>001</t>
-  </si>
-  <si>
     <t>818</t>
   </si>
   <si>
@@ -184,18 +184,18 @@
     <t>IOT</t>
   </si>
   <si>
+    <t>Sub-Saharan Africa</t>
+  </si>
+  <si>
     <t>014</t>
   </si>
   <si>
+    <t>202</t>
+  </si>
+  <si>
     <t>Eastern Africa</t>
   </si>
   <si>
-    <t>202</t>
-  </si>
-  <si>
-    <t>Sub-Saharan Africa</t>
-  </si>
-  <si>
     <t>IO</t>
   </si>
   <si>
@@ -850,27 +850,27 @@
     <t>AIA</t>
   </si>
   <si>
+    <t>Latin America and the Caribbean</t>
+  </si>
+  <si>
     <t>029</t>
   </si>
   <si>
+    <t>419</t>
+  </si>
+  <si>
+    <t>019</t>
+  </si>
+  <si>
     <t>Caribbean</t>
   </si>
   <si>
+    <t>AI</t>
+  </si>
+  <si>
     <t>Americas</t>
   </si>
   <si>
-    <t>019</t>
-  </si>
-  <si>
-    <t>419</t>
-  </si>
-  <si>
-    <t>Latin America and the Caribbean</t>
-  </si>
-  <si>
-    <t>AI</t>
-  </si>
-  <si>
     <t>028</t>
   </si>
   <si>
@@ -1504,12 +1504,12 @@
     <t>BMU</t>
   </si>
   <si>
+    <t>Northern America</t>
+  </si>
+  <si>
     <t>021</t>
   </si>
   <si>
-    <t>Northern America</t>
-  </si>
-  <si>
     <t>BM</t>
   </si>
   <si>
@@ -1582,21 +1582,21 @@
     <t>KAZ</t>
   </si>
   <si>
+    <t>Central Asia</t>
+  </si>
+  <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t>142</t>
+  </si>
+  <si>
+    <t>KZ</t>
+  </si>
+  <si>
     <t>Asia</t>
   </si>
   <si>
-    <t>142</t>
-  </si>
-  <si>
-    <t>143</t>
-  </si>
-  <si>
-    <t>Central Asia</t>
-  </si>
-  <si>
-    <t>KZ</t>
-  </si>
-  <si>
     <t>417</t>
   </si>
   <si>
@@ -1654,12 +1654,12 @@
     <t>CHN</t>
   </si>
   <si>
+    <t>Eastern Asia</t>
+  </si>
+  <si>
     <t>030</t>
   </si>
   <si>
-    <t>Eastern Asia</t>
-  </si>
-  <si>
     <t>CN</t>
   </si>
   <si>
@@ -1744,12 +1744,12 @@
     <t>BRN</t>
   </si>
   <si>
+    <t>South-eastern Asia</t>
+  </si>
+  <si>
     <t>035</t>
   </si>
   <si>
-    <t>South-eastern Asia</t>
-  </si>
-  <si>
     <t>BN</t>
   </si>
   <si>
@@ -1882,12 +1882,12 @@
     <t>AFG</t>
   </si>
   <si>
+    <t>Southern Asia</t>
+  </si>
+  <si>
     <t>034</t>
   </si>
   <si>
-    <t>Southern Asia</t>
-  </si>
-  <si>
     <t>AF</t>
   </si>
   <si>
@@ -1996,12 +1996,12 @@
     <t>ARM</t>
   </si>
   <si>
+    <t>Western Asia</t>
+  </si>
+  <si>
     <t>145</t>
   </si>
   <si>
-    <t>Western Asia</t>
-  </si>
-  <si>
     <t>AM</t>
   </si>
   <si>
@@ -2218,21 +2218,21 @@
     <t>BLR</t>
   </si>
   <si>
+    <t>Eastern Europe</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>BY</t>
+  </si>
+  <si>
     <t>Europe</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>Eastern Europe</t>
-  </si>
-  <si>
-    <t>BY</t>
-  </si>
-  <si>
     <t>100</t>
   </si>
   <si>
@@ -2350,12 +2350,12 @@
     <t>ALA</t>
   </si>
   <si>
+    <t>Northern Europe</t>
+  </si>
+  <si>
     <t>154</t>
   </si>
   <si>
-    <t>Northern Europe</t>
-  </si>
-  <si>
     <t>AX</t>
   </si>
   <si>
@@ -2560,12 +2560,12 @@
     <t>ALB</t>
   </si>
   <si>
+    <t>Southern Europe</t>
+  </si>
+  <si>
     <t>039</t>
   </si>
   <si>
-    <t>Southern Europe</t>
-  </si>
-  <si>
     <t>AL</t>
   </si>
   <si>
@@ -2758,12 +2758,12 @@
     <t>AUT</t>
   </si>
   <si>
+    <t>Western Europe</t>
+  </si>
+  <si>
     <t>155</t>
   </si>
   <si>
-    <t>Western Europe</t>
-  </si>
-  <si>
     <t>AT</t>
   </si>
   <si>
@@ -2872,21 +2872,21 @@
     <t>AUS</t>
   </si>
   <si>
+    <t>Australia and New Zealand</t>
+  </si>
+  <si>
+    <t>053</t>
+  </si>
+  <si>
+    <t>009</t>
+  </si>
+  <si>
+    <t>AU</t>
+  </si>
+  <si>
     <t>Oceania</t>
   </si>
   <si>
-    <t>009</t>
-  </si>
-  <si>
-    <t>053</t>
-  </si>
-  <si>
-    <t>Australia and New Zealand</t>
-  </si>
-  <si>
-    <t>AU</t>
-  </si>
-  <si>
     <t>162</t>
   </si>
   <si>
@@ -2956,12 +2956,12 @@
     <t>FJI</t>
   </si>
   <si>
+    <t>Melanesia</t>
+  </si>
+  <si>
     <t>054</t>
   </si>
   <si>
-    <t>Melanesia</t>
-  </si>
-  <si>
     <t>FJ</t>
   </si>
   <si>
@@ -3022,12 +3022,12 @@
     <t>GUM</t>
   </si>
   <si>
+    <t>Micronesia</t>
+  </si>
+  <si>
     <t>057</t>
   </si>
   <si>
-    <t>Micronesia</t>
-  </si>
-  <si>
     <t>GU</t>
   </si>
   <si>
@@ -3124,10 +3124,10 @@
     <t>ASM</t>
   </si>
   <si>
+    <t>Polynesia</t>
+  </si>
+  <si>
     <t>061</t>
-  </si>
-  <si>
-    <t>Polynesia</t>
   </si>
   <si>
     <t>AS</t>
@@ -4611,16 +4611,16 @@
       <c r="LT2" t="s">
         <v>21</v>
       </c>
+      <c r="LU2" t="s">
+        <v>22</v>
+      </c>
       <c r="LW2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="LX2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="LY2" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ2" t="s">
         <v>25</v>
       </c>
       <c r="MA2" t="s">
@@ -4646,23 +4646,23 @@
       <c r="LT3" t="s">
         <v>31</v>
       </c>
+      <c r="LU3" t="s">
+        <v>22</v>
+      </c>
       <c r="LW3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="LX3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="LY3" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ3" t="s">
         <v>25</v>
       </c>
       <c r="MA3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="MB3" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="MC3" t="s">
         <v>28</v>
@@ -4681,23 +4681,23 @@
       <c r="LT4" t="s">
         <v>35</v>
       </c>
+      <c r="LU4" t="s">
+        <v>22</v>
+      </c>
       <c r="LW4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="LX4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="LY4" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ4" t="s">
         <v>25</v>
       </c>
       <c r="MA4" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="MB4" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="MC4" t="s">
         <v>28</v>
@@ -4716,23 +4716,23 @@
       <c r="LT5" t="s">
         <v>39</v>
       </c>
+      <c r="LU5" t="s">
+        <v>22</v>
+      </c>
       <c r="LW5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="LX5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="LY5" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ5" t="s">
         <v>25</v>
       </c>
       <c r="MA5" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="MB5" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="MC5" t="s">
         <v>28</v>
@@ -4751,23 +4751,23 @@
       <c r="LT6" t="s">
         <v>43</v>
       </c>
+      <c r="LU6" t="s">
+        <v>22</v>
+      </c>
       <c r="LW6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="LX6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="LY6" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ6" t="s">
         <v>25</v>
       </c>
       <c r="MA6" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="MB6" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="MC6" t="s">
         <v>28</v>
@@ -4786,23 +4786,23 @@
       <c r="LT7" t="s">
         <v>47</v>
       </c>
+      <c r="LU7" t="s">
+        <v>22</v>
+      </c>
       <c r="LW7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="LX7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="LY7" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ7" t="s">
         <v>25</v>
       </c>
       <c r="MA7" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="MB7" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="MC7" t="s">
         <v>28</v>
@@ -4821,23 +4821,23 @@
       <c r="LT8" t="s">
         <v>51</v>
       </c>
+      <c r="LU8" t="s">
+        <v>22</v>
+      </c>
       <c r="LW8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="LX8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="LY8" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ8" t="s">
         <v>25</v>
       </c>
       <c r="MA8" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="MB8" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="MC8" t="s">
         <v>28</v>
@@ -4863,22 +4863,22 @@
         <v>57</v>
       </c>
       <c r="LW9" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="LX9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="LY9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="LZ9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="MA9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="MB9" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="MC9" t="s">
         <v>28</v>
@@ -4904,22 +4904,22 @@
         <v>57</v>
       </c>
       <c r="LW10" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="LX10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="LY10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="LZ10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="MA10" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="MB10" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="MC10" t="s">
         <v>28</v>
@@ -4945,22 +4945,22 @@
         <v>57</v>
       </c>
       <c r="LW11" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="LX11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="LY11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="LZ11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="MA11" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="MB11" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="MC11" t="s">
         <v>28</v>
@@ -4986,22 +4986,22 @@
         <v>57</v>
       </c>
       <c r="LW12" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="LX12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="LY12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="LZ12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="MA12" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="MB12" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="MC12" t="s">
         <v>28</v>
@@ -5027,22 +5027,22 @@
         <v>57</v>
       </c>
       <c r="LW13" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="LX13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="LY13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="LZ13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="MA13" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="MB13" t="s">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="MC13" t="s">
         <v>28</v>
@@ -5068,22 +5068,22 @@
         <v>57</v>
       </c>
       <c r="LW14" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="LX14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="LY14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="LZ14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="MA14" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="MB14" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="MC14" t="s">
         <v>28</v>
@@ -5109,22 +5109,22 @@
         <v>57</v>
       </c>
       <c r="LW15" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="LX15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="LY15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="LZ15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="MA15" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="MB15" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="MC15" t="s">
         <v>28</v>
@@ -5150,22 +5150,22 @@
         <v>57</v>
       </c>
       <c r="LW16" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="LX16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="LY16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="LZ16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="MA16" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="MB16" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="MC16" t="s">
         <v>28</v>
@@ -5191,22 +5191,22 @@
         <v>57</v>
       </c>
       <c r="LW17" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="LX17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="LY17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="LZ17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="MA17" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="MB17" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="MC17" t="s">
         <v>28</v>
@@ -5232,22 +5232,22 @@
         <v>57</v>
       </c>
       <c r="LW18" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="LX18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="LY18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="LZ18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="MA18" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="MB18" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="MC18" t="s">
         <v>28</v>
@@ -5273,22 +5273,22 @@
         <v>57</v>
       </c>
       <c r="LW19" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="LX19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="LY19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="LZ19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="MA19" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="MB19" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="MC19" t="s">
         <v>28</v>
@@ -5314,22 +5314,22 @@
         <v>57</v>
       </c>
       <c r="LW20" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="LX20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="LY20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="LZ20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="MA20" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="MB20" t="s">
-        <v>104</v>
+        <v>27</v>
       </c>
       <c r="MC20" t="s">
         <v>28</v>
@@ -5355,22 +5355,22 @@
         <v>57</v>
       </c>
       <c r="LW21" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="LX21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="LY21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="LZ21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="MA21" t="s">
-        <v>59</v>
+        <v>108</v>
       </c>
       <c r="MB21" t="s">
-        <v>108</v>
+        <v>27</v>
       </c>
       <c r="MC21" t="s">
         <v>28</v>
@@ -5396,22 +5396,22 @@
         <v>57</v>
       </c>
       <c r="LW22" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="LX22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="LY22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="LZ22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="MA22" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="MB22" t="s">
-        <v>112</v>
+        <v>27</v>
       </c>
       <c r="MC22" t="s">
         <v>28</v>
@@ -5437,22 +5437,22 @@
         <v>57</v>
       </c>
       <c r="LW23" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="LX23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="LY23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="LZ23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="MA23" t="s">
-        <v>59</v>
+        <v>116</v>
       </c>
       <c r="MB23" t="s">
-        <v>116</v>
+        <v>27</v>
       </c>
       <c r="MC23" t="s">
         <v>28</v>
@@ -5478,22 +5478,22 @@
         <v>57</v>
       </c>
       <c r="LW24" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="LX24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="LY24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="LZ24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="MA24" t="s">
-        <v>59</v>
+        <v>120</v>
       </c>
       <c r="MB24" t="s">
-        <v>120</v>
+        <v>27</v>
       </c>
       <c r="MC24" t="s">
         <v>28</v>
@@ -5519,22 +5519,22 @@
         <v>57</v>
       </c>
       <c r="LW25" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="LX25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="LY25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="LZ25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="MA25" t="s">
-        <v>59</v>
+        <v>124</v>
       </c>
       <c r="MB25" t="s">
-        <v>124</v>
+        <v>27</v>
       </c>
       <c r="MC25" t="s">
         <v>28</v>
@@ -5560,22 +5560,22 @@
         <v>57</v>
       </c>
       <c r="LW26" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="LX26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="LY26" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="LZ26" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="MA26" t="s">
-        <v>59</v>
+        <v>128</v>
       </c>
       <c r="MB26" t="s">
-        <v>128</v>
+        <v>27</v>
       </c>
       <c r="MC26" t="s">
         <v>28</v>
@@ -5601,22 +5601,22 @@
         <v>57</v>
       </c>
       <c r="LW27" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="LX27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="LY27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="LZ27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="MA27" t="s">
-        <v>59</v>
+        <v>132</v>
       </c>
       <c r="MB27" t="s">
-        <v>132</v>
+        <v>27</v>
       </c>
       <c r="MC27" t="s">
         <v>28</v>
@@ -5642,22 +5642,22 @@
         <v>57</v>
       </c>
       <c r="LW28" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="LX28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="LY28" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="LZ28" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="MA28" t="s">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="MB28" t="s">
-        <v>136</v>
+        <v>27</v>
       </c>
       <c r="MC28" t="s">
         <v>28</v>
@@ -5683,22 +5683,22 @@
         <v>57</v>
       </c>
       <c r="LW29" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="LX29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="LY29" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="LZ29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="MA29" t="s">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="MB29" t="s">
-        <v>140</v>
+        <v>27</v>
       </c>
       <c r="MC29" t="s">
         <v>28</v>
@@ -5724,22 +5724,22 @@
         <v>57</v>
       </c>
       <c r="LW30" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="LX30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="LY30" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="LZ30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="MA30" t="s">
-        <v>59</v>
+        <v>144</v>
       </c>
       <c r="MB30" t="s">
-        <v>144</v>
+        <v>27</v>
       </c>
       <c r="MC30" t="s">
         <v>28</v>
@@ -5759,28 +5759,28 @@
         <v>147</v>
       </c>
       <c r="LU31" t="s">
+        <v>56</v>
+      </c>
+      <c r="LV31" t="s">
         <v>148</v>
       </c>
-      <c r="LV31" t="s">
+      <c r="LW31" t="s">
+        <v>58</v>
+      </c>
+      <c r="LX31" t="s">
+        <v>24</v>
+      </c>
+      <c r="LY31" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ31" t="s">
         <v>149</v>
       </c>
-      <c r="LW31" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX31" t="s">
-        <v>23</v>
-      </c>
-      <c r="LY31" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ31" t="s">
-        <v>58</v>
-      </c>
       <c r="MA31" t="s">
-        <v>59</v>
+        <v>150</v>
       </c>
       <c r="MB31" t="s">
-        <v>150</v>
+        <v>27</v>
       </c>
       <c r="MC31" t="s">
         <v>28</v>
@@ -5800,28 +5800,28 @@
         <v>153</v>
       </c>
       <c r="LU32" t="s">
+        <v>56</v>
+      </c>
+      <c r="LV32" t="s">
         <v>148</v>
       </c>
-      <c r="LV32" t="s">
+      <c r="LW32" t="s">
+        <v>58</v>
+      </c>
+      <c r="LX32" t="s">
+        <v>24</v>
+      </c>
+      <c r="LY32" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ32" t="s">
         <v>149</v>
       </c>
-      <c r="LW32" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX32" t="s">
-        <v>23</v>
-      </c>
-      <c r="LY32" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ32" t="s">
-        <v>58</v>
-      </c>
       <c r="MA32" t="s">
-        <v>59</v>
+        <v>154</v>
       </c>
       <c r="MB32" t="s">
-        <v>154</v>
+        <v>27</v>
       </c>
       <c r="MC32" t="s">
         <v>28</v>
@@ -5841,28 +5841,28 @@
         <v>157</v>
       </c>
       <c r="LU33" t="s">
+        <v>56</v>
+      </c>
+      <c r="LV33" t="s">
         <v>148</v>
       </c>
-      <c r="LV33" t="s">
+      <c r="LW33" t="s">
+        <v>58</v>
+      </c>
+      <c r="LX33" t="s">
+        <v>24</v>
+      </c>
+      <c r="LY33" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ33" t="s">
         <v>149</v>
       </c>
-      <c r="LW33" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX33" t="s">
-        <v>23</v>
-      </c>
-      <c r="LY33" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ33" t="s">
-        <v>58</v>
-      </c>
       <c r="MA33" t="s">
-        <v>59</v>
+        <v>158</v>
       </c>
       <c r="MB33" t="s">
-        <v>158</v>
+        <v>27</v>
       </c>
       <c r="MC33" t="s">
         <v>28</v>
@@ -5882,28 +5882,28 @@
         <v>161</v>
       </c>
       <c r="LU34" t="s">
+        <v>56</v>
+      </c>
+      <c r="LV34" t="s">
         <v>148</v>
       </c>
-      <c r="LV34" t="s">
+      <c r="LW34" t="s">
+        <v>58</v>
+      </c>
+      <c r="LX34" t="s">
+        <v>24</v>
+      </c>
+      <c r="LY34" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ34" t="s">
         <v>149</v>
       </c>
-      <c r="LW34" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX34" t="s">
-        <v>23</v>
-      </c>
-      <c r="LY34" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ34" t="s">
-        <v>58</v>
-      </c>
       <c r="MA34" t="s">
-        <v>59</v>
+        <v>162</v>
       </c>
       <c r="MB34" t="s">
-        <v>162</v>
+        <v>27</v>
       </c>
       <c r="MC34" t="s">
         <v>28</v>
@@ -5923,28 +5923,28 @@
         <v>165</v>
       </c>
       <c r="LU35" t="s">
+        <v>56</v>
+      </c>
+      <c r="LV35" t="s">
         <v>148</v>
       </c>
-      <c r="LV35" t="s">
+      <c r="LW35" t="s">
+        <v>58</v>
+      </c>
+      <c r="LX35" t="s">
+        <v>24</v>
+      </c>
+      <c r="LY35" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ35" t="s">
         <v>149</v>
       </c>
-      <c r="LW35" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX35" t="s">
-        <v>23</v>
-      </c>
-      <c r="LY35" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ35" t="s">
-        <v>58</v>
-      </c>
       <c r="MA35" t="s">
-        <v>59</v>
+        <v>166</v>
       </c>
       <c r="MB35" t="s">
-        <v>166</v>
+        <v>27</v>
       </c>
       <c r="MC35" t="s">
         <v>28</v>
@@ -5964,28 +5964,28 @@
         <v>169</v>
       </c>
       <c r="LU36" t="s">
+        <v>56</v>
+      </c>
+      <c r="LV36" t="s">
         <v>148</v>
       </c>
-      <c r="LV36" t="s">
+      <c r="LW36" t="s">
+        <v>58</v>
+      </c>
+      <c r="LX36" t="s">
+        <v>24</v>
+      </c>
+      <c r="LY36" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ36" t="s">
         <v>149</v>
       </c>
-      <c r="LW36" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX36" t="s">
-        <v>23</v>
-      </c>
-      <c r="LY36" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ36" t="s">
-        <v>58</v>
-      </c>
       <c r="MA36" t="s">
-        <v>59</v>
+        <v>170</v>
       </c>
       <c r="MB36" t="s">
-        <v>170</v>
+        <v>27</v>
       </c>
       <c r="MC36" t="s">
         <v>28</v>
@@ -6005,28 +6005,28 @@
         <v>173</v>
       </c>
       <c r="LU37" t="s">
+        <v>56</v>
+      </c>
+      <c r="LV37" t="s">
         <v>148</v>
       </c>
-      <c r="LV37" t="s">
+      <c r="LW37" t="s">
+        <v>58</v>
+      </c>
+      <c r="LX37" t="s">
+        <v>24</v>
+      </c>
+      <c r="LY37" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ37" t="s">
         <v>149</v>
       </c>
-      <c r="LW37" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX37" t="s">
-        <v>23</v>
-      </c>
-      <c r="LY37" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ37" t="s">
-        <v>58</v>
-      </c>
       <c r="MA37" t="s">
-        <v>59</v>
+        <v>174</v>
       </c>
       <c r="MB37" t="s">
-        <v>174</v>
+        <v>27</v>
       </c>
       <c r="MC37" t="s">
         <v>28</v>
@@ -6046,28 +6046,28 @@
         <v>177</v>
       </c>
       <c r="LU38" t="s">
+        <v>56</v>
+      </c>
+      <c r="LV38" t="s">
         <v>148</v>
       </c>
-      <c r="LV38" t="s">
+      <c r="LW38" t="s">
+        <v>58</v>
+      </c>
+      <c r="LX38" t="s">
+        <v>24</v>
+      </c>
+      <c r="LY38" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ38" t="s">
         <v>149</v>
       </c>
-      <c r="LW38" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX38" t="s">
-        <v>23</v>
-      </c>
-      <c r="LY38" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ38" t="s">
-        <v>58</v>
-      </c>
       <c r="MA38" t="s">
-        <v>59</v>
+        <v>178</v>
       </c>
       <c r="MB38" t="s">
-        <v>178</v>
+        <v>27</v>
       </c>
       <c r="MC38" t="s">
         <v>28</v>
@@ -6087,28 +6087,28 @@
         <v>181</v>
       </c>
       <c r="LU39" t="s">
+        <v>56</v>
+      </c>
+      <c r="LV39" t="s">
         <v>148</v>
       </c>
-      <c r="LV39" t="s">
+      <c r="LW39" t="s">
+        <v>58</v>
+      </c>
+      <c r="LX39" t="s">
+        <v>24</v>
+      </c>
+      <c r="LY39" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ39" t="s">
         <v>149</v>
       </c>
-      <c r="LW39" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX39" t="s">
-        <v>23</v>
-      </c>
-      <c r="LY39" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ39" t="s">
-        <v>58</v>
-      </c>
       <c r="MA39" t="s">
-        <v>59</v>
+        <v>182</v>
       </c>
       <c r="MB39" t="s">
-        <v>182</v>
+        <v>27</v>
       </c>
       <c r="MC39" t="s">
         <v>28</v>
@@ -6128,28 +6128,28 @@
         <v>185</v>
       </c>
       <c r="LU40" t="s">
+        <v>56</v>
+      </c>
+      <c r="LV40" t="s">
         <v>186</v>
       </c>
-      <c r="LV40" t="s">
+      <c r="LW40" t="s">
+        <v>58</v>
+      </c>
+      <c r="LX40" t="s">
+        <v>24</v>
+      </c>
+      <c r="LY40" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ40" t="s">
         <v>187</v>
       </c>
-      <c r="LW40" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX40" t="s">
-        <v>23</v>
-      </c>
-      <c r="LY40" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ40" t="s">
-        <v>58</v>
-      </c>
       <c r="MA40" t="s">
-        <v>59</v>
+        <v>188</v>
       </c>
       <c r="MB40" t="s">
-        <v>188</v>
+        <v>27</v>
       </c>
       <c r="MC40" t="s">
         <v>28</v>
@@ -6169,28 +6169,28 @@
         <v>191</v>
       </c>
       <c r="LU41" t="s">
+        <v>56</v>
+      </c>
+      <c r="LV41" t="s">
         <v>186</v>
       </c>
-      <c r="LV41" t="s">
+      <c r="LW41" t="s">
+        <v>58</v>
+      </c>
+      <c r="LX41" t="s">
+        <v>24</v>
+      </c>
+      <c r="LY41" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ41" t="s">
         <v>187</v>
       </c>
-      <c r="LW41" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX41" t="s">
-        <v>23</v>
-      </c>
-      <c r="LY41" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ41" t="s">
-        <v>58</v>
-      </c>
       <c r="MA41" t="s">
-        <v>59</v>
+        <v>192</v>
       </c>
       <c r="MB41" t="s">
-        <v>192</v>
+        <v>27</v>
       </c>
       <c r="MC41" t="s">
         <v>28</v>
@@ -6210,28 +6210,28 @@
         <v>195</v>
       </c>
       <c r="LU42" t="s">
+        <v>56</v>
+      </c>
+      <c r="LV42" t="s">
         <v>186</v>
       </c>
-      <c r="LV42" t="s">
+      <c r="LW42" t="s">
+        <v>58</v>
+      </c>
+      <c r="LX42" t="s">
+        <v>24</v>
+      </c>
+      <c r="LY42" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ42" t="s">
         <v>187</v>
       </c>
-      <c r="LW42" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX42" t="s">
-        <v>23</v>
-      </c>
-      <c r="LY42" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ42" t="s">
-        <v>58</v>
-      </c>
       <c r="MA42" t="s">
-        <v>59</v>
+        <v>196</v>
       </c>
       <c r="MB42" t="s">
-        <v>196</v>
+        <v>27</v>
       </c>
       <c r="MC42" t="s">
         <v>28</v>
@@ -6251,28 +6251,28 @@
         <v>199</v>
       </c>
       <c r="LU43" t="s">
+        <v>56</v>
+      </c>
+      <c r="LV43" t="s">
         <v>186</v>
       </c>
-      <c r="LV43" t="s">
+      <c r="LW43" t="s">
+        <v>58</v>
+      </c>
+      <c r="LX43" t="s">
+        <v>24</v>
+      </c>
+      <c r="LY43" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ43" t="s">
         <v>187</v>
       </c>
-      <c r="LW43" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX43" t="s">
-        <v>23</v>
-      </c>
-      <c r="LY43" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ43" t="s">
-        <v>58</v>
-      </c>
       <c r="MA43" t="s">
-        <v>59</v>
+        <v>200</v>
       </c>
       <c r="MB43" t="s">
-        <v>200</v>
+        <v>27</v>
       </c>
       <c r="MC43" t="s">
         <v>28</v>
@@ -6292,28 +6292,28 @@
         <v>203</v>
       </c>
       <c r="LU44" t="s">
+        <v>56</v>
+      </c>
+      <c r="LV44" t="s">
         <v>186</v>
       </c>
-      <c r="LV44" t="s">
+      <c r="LW44" t="s">
+        <v>58</v>
+      </c>
+      <c r="LX44" t="s">
+        <v>24</v>
+      </c>
+      <c r="LY44" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ44" t="s">
         <v>187</v>
       </c>
-      <c r="LW44" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX44" t="s">
-        <v>23</v>
-      </c>
-      <c r="LY44" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ44" t="s">
-        <v>58</v>
-      </c>
       <c r="MA44" t="s">
-        <v>59</v>
+        <v>204</v>
       </c>
       <c r="MB44" t="s">
-        <v>204</v>
+        <v>27</v>
       </c>
       <c r="MC44" t="s">
         <v>28</v>
@@ -6333,28 +6333,28 @@
         <v>207</v>
       </c>
       <c r="LU45" t="s">
+        <v>56</v>
+      </c>
+      <c r="LV45" t="s">
         <v>208</v>
       </c>
-      <c r="LV45" t="s">
+      <c r="LW45" t="s">
+        <v>58</v>
+      </c>
+      <c r="LX45" t="s">
+        <v>24</v>
+      </c>
+      <c r="LY45" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ45" t="s">
         <v>209</v>
       </c>
-      <c r="LW45" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX45" t="s">
-        <v>23</v>
-      </c>
-      <c r="LY45" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ45" t="s">
-        <v>58</v>
-      </c>
       <c r="MA45" t="s">
-        <v>59</v>
+        <v>210</v>
       </c>
       <c r="MB45" t="s">
-        <v>210</v>
+        <v>27</v>
       </c>
       <c r="MC45" t="s">
         <v>28</v>
@@ -6374,28 +6374,28 @@
         <v>213</v>
       </c>
       <c r="LU46" t="s">
+        <v>56</v>
+      </c>
+      <c r="LV46" t="s">
         <v>208</v>
       </c>
-      <c r="LV46" t="s">
+      <c r="LW46" t="s">
+        <v>58</v>
+      </c>
+      <c r="LX46" t="s">
+        <v>24</v>
+      </c>
+      <c r="LY46" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ46" t="s">
         <v>209</v>
       </c>
-      <c r="LW46" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX46" t="s">
-        <v>23</v>
-      </c>
-      <c r="LY46" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ46" t="s">
-        <v>58</v>
-      </c>
       <c r="MA46" t="s">
-        <v>59</v>
+        <v>214</v>
       </c>
       <c r="MB46" t="s">
-        <v>214</v>
+        <v>27</v>
       </c>
       <c r="MC46" t="s">
         <v>28</v>
@@ -6415,28 +6415,28 @@
         <v>217</v>
       </c>
       <c r="LU47" t="s">
+        <v>56</v>
+      </c>
+      <c r="LV47" t="s">
         <v>208</v>
       </c>
-      <c r="LV47" t="s">
+      <c r="LW47" t="s">
+        <v>58</v>
+      </c>
+      <c r="LX47" t="s">
+        <v>24</v>
+      </c>
+      <c r="LY47" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ47" t="s">
         <v>209</v>
       </c>
-      <c r="LW47" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX47" t="s">
-        <v>23</v>
-      </c>
-      <c r="LY47" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ47" t="s">
-        <v>58</v>
-      </c>
       <c r="MA47" t="s">
-        <v>59</v>
+        <v>218</v>
       </c>
       <c r="MB47" t="s">
-        <v>218</v>
+        <v>27</v>
       </c>
       <c r="MC47" t="s">
         <v>28</v>
@@ -6456,28 +6456,28 @@
         <v>221</v>
       </c>
       <c r="LU48" t="s">
+        <v>56</v>
+      </c>
+      <c r="LV48" t="s">
         <v>208</v>
       </c>
-      <c r="LV48" t="s">
+      <c r="LW48" t="s">
+        <v>58</v>
+      </c>
+      <c r="LX48" t="s">
+        <v>24</v>
+      </c>
+      <c r="LY48" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ48" t="s">
         <v>209</v>
       </c>
-      <c r="LW48" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX48" t="s">
-        <v>23</v>
-      </c>
-      <c r="LY48" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ48" t="s">
-        <v>58</v>
-      </c>
       <c r="MA48" t="s">
-        <v>59</v>
+        <v>222</v>
       </c>
       <c r="MB48" t="s">
-        <v>222</v>
+        <v>27</v>
       </c>
       <c r="MC48" t="s">
         <v>28</v>
@@ -6497,28 +6497,28 @@
         <v>225</v>
       </c>
       <c r="LU49" t="s">
+        <v>56</v>
+      </c>
+      <c r="LV49" t="s">
         <v>208</v>
       </c>
-      <c r="LV49" t="s">
+      <c r="LW49" t="s">
+        <v>58</v>
+      </c>
+      <c r="LX49" t="s">
+        <v>24</v>
+      </c>
+      <c r="LY49" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ49" t="s">
         <v>209</v>
       </c>
-      <c r="LW49" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX49" t="s">
-        <v>23</v>
-      </c>
-      <c r="LY49" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ49" t="s">
-        <v>58</v>
-      </c>
       <c r="MA49" t="s">
-        <v>59</v>
+        <v>226</v>
       </c>
       <c r="MB49" t="s">
-        <v>226</v>
+        <v>27</v>
       </c>
       <c r="MC49" t="s">
         <v>28</v>
@@ -6538,28 +6538,28 @@
         <v>229</v>
       </c>
       <c r="LU50" t="s">
+        <v>56</v>
+      </c>
+      <c r="LV50" t="s">
         <v>208</v>
       </c>
-      <c r="LV50" t="s">
+      <c r="LW50" t="s">
+        <v>58</v>
+      </c>
+      <c r="LX50" t="s">
+        <v>24</v>
+      </c>
+      <c r="LY50" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ50" t="s">
         <v>209</v>
       </c>
-      <c r="LW50" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX50" t="s">
-        <v>23</v>
-      </c>
-      <c r="LY50" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ50" t="s">
-        <v>58</v>
-      </c>
       <c r="MA50" t="s">
-        <v>59</v>
+        <v>230</v>
       </c>
       <c r="MB50" t="s">
-        <v>230</v>
+        <v>27</v>
       </c>
       <c r="MC50" t="s">
         <v>28</v>
@@ -6579,28 +6579,28 @@
         <v>233</v>
       </c>
       <c r="LU51" t="s">
+        <v>56</v>
+      </c>
+      <c r="LV51" t="s">
         <v>208</v>
       </c>
-      <c r="LV51" t="s">
+      <c r="LW51" t="s">
+        <v>58</v>
+      </c>
+      <c r="LX51" t="s">
+        <v>24</v>
+      </c>
+      <c r="LY51" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ51" t="s">
         <v>209</v>
       </c>
-      <c r="LW51" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX51" t="s">
-        <v>23</v>
-      </c>
-      <c r="LY51" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ51" t="s">
-        <v>58</v>
-      </c>
       <c r="MA51" t="s">
-        <v>59</v>
+        <v>234</v>
       </c>
       <c r="MB51" t="s">
-        <v>234</v>
+        <v>27</v>
       </c>
       <c r="MC51" t="s">
         <v>28</v>
@@ -6620,28 +6620,28 @@
         <v>237</v>
       </c>
       <c r="LU52" t="s">
+        <v>56</v>
+      </c>
+      <c r="LV52" t="s">
         <v>208</v>
       </c>
-      <c r="LV52" t="s">
+      <c r="LW52" t="s">
+        <v>58</v>
+      </c>
+      <c r="LX52" t="s">
+        <v>24</v>
+      </c>
+      <c r="LY52" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ52" t="s">
         <v>209</v>
       </c>
-      <c r="LW52" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX52" t="s">
-        <v>23</v>
-      </c>
-      <c r="LY52" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ52" t="s">
-        <v>58</v>
-      </c>
       <c r="MA52" t="s">
-        <v>59</v>
+        <v>238</v>
       </c>
       <c r="MB52" t="s">
-        <v>238</v>
+        <v>27</v>
       </c>
       <c r="MC52" t="s">
         <v>28</v>
@@ -6661,28 +6661,28 @@
         <v>241</v>
       </c>
       <c r="LU53" t="s">
+        <v>56</v>
+      </c>
+      <c r="LV53" t="s">
         <v>208</v>
       </c>
-      <c r="LV53" t="s">
+      <c r="LW53" t="s">
+        <v>58</v>
+      </c>
+      <c r="LX53" t="s">
+        <v>24</v>
+      </c>
+      <c r="LY53" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ53" t="s">
         <v>209</v>
       </c>
-      <c r="LW53" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX53" t="s">
-        <v>23</v>
-      </c>
-      <c r="LY53" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ53" t="s">
-        <v>58</v>
-      </c>
       <c r="MA53" t="s">
-        <v>59</v>
+        <v>242</v>
       </c>
       <c r="MB53" t="s">
-        <v>242</v>
+        <v>27</v>
       </c>
       <c r="MC53" t="s">
         <v>28</v>
@@ -6702,28 +6702,28 @@
         <v>245</v>
       </c>
       <c r="LU54" t="s">
+        <v>56</v>
+      </c>
+      <c r="LV54" t="s">
         <v>208</v>
       </c>
-      <c r="LV54" t="s">
+      <c r="LW54" t="s">
+        <v>58</v>
+      </c>
+      <c r="LX54" t="s">
+        <v>24</v>
+      </c>
+      <c r="LY54" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ54" t="s">
         <v>209</v>
       </c>
-      <c r="LW54" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX54" t="s">
-        <v>23</v>
-      </c>
-      <c r="LY54" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ54" t="s">
-        <v>58</v>
-      </c>
       <c r="MA54" t="s">
-        <v>59</v>
+        <v>246</v>
       </c>
       <c r="MB54" t="s">
-        <v>246</v>
+        <v>27</v>
       </c>
       <c r="MC54" t="s">
         <v>28</v>
@@ -6743,28 +6743,28 @@
         <v>249</v>
       </c>
       <c r="LU55" t="s">
+        <v>56</v>
+      </c>
+      <c r="LV55" t="s">
         <v>208</v>
       </c>
-      <c r="LV55" t="s">
+      <c r="LW55" t="s">
+        <v>58</v>
+      </c>
+      <c r="LX55" t="s">
+        <v>24</v>
+      </c>
+      <c r="LY55" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ55" t="s">
         <v>209</v>
       </c>
-      <c r="LW55" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX55" t="s">
-        <v>23</v>
-      </c>
-      <c r="LY55" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ55" t="s">
-        <v>58</v>
-      </c>
       <c r="MA55" t="s">
-        <v>59</v>
+        <v>250</v>
       </c>
       <c r="MB55" t="s">
-        <v>250</v>
+        <v>27</v>
       </c>
       <c r="MC55" t="s">
         <v>28</v>
@@ -6784,28 +6784,28 @@
         <v>253</v>
       </c>
       <c r="LU56" t="s">
+        <v>56</v>
+      </c>
+      <c r="LV56" t="s">
         <v>208</v>
       </c>
-      <c r="LV56" t="s">
+      <c r="LW56" t="s">
+        <v>58</v>
+      </c>
+      <c r="LX56" t="s">
+        <v>24</v>
+      </c>
+      <c r="LY56" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ56" t="s">
         <v>209</v>
       </c>
-      <c r="LW56" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX56" t="s">
-        <v>23</v>
-      </c>
-      <c r="LY56" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ56" t="s">
-        <v>58</v>
-      </c>
       <c r="MA56" t="s">
-        <v>59</v>
+        <v>254</v>
       </c>
       <c r="MB56" t="s">
-        <v>254</v>
+        <v>27</v>
       </c>
       <c r="MC56" t="s">
         <v>28</v>
@@ -6825,28 +6825,28 @@
         <v>257</v>
       </c>
       <c r="LU57" t="s">
+        <v>56</v>
+      </c>
+      <c r="LV57" t="s">
         <v>208</v>
       </c>
-      <c r="LV57" t="s">
+      <c r="LW57" t="s">
+        <v>58</v>
+      </c>
+      <c r="LX57" t="s">
+        <v>24</v>
+      </c>
+      <c r="LY57" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ57" t="s">
         <v>209</v>
       </c>
-      <c r="LW57" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX57" t="s">
-        <v>23</v>
-      </c>
-      <c r="LY57" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ57" t="s">
-        <v>58</v>
-      </c>
       <c r="MA57" t="s">
-        <v>59</v>
+        <v>258</v>
       </c>
       <c r="MB57" t="s">
-        <v>258</v>
+        <v>27</v>
       </c>
       <c r="MC57" t="s">
         <v>28</v>
@@ -6866,28 +6866,28 @@
         <v>261</v>
       </c>
       <c r="LU58" t="s">
+        <v>56</v>
+      </c>
+      <c r="LV58" t="s">
         <v>208</v>
       </c>
-      <c r="LV58" t="s">
+      <c r="LW58" t="s">
+        <v>58</v>
+      </c>
+      <c r="LX58" t="s">
+        <v>24</v>
+      </c>
+      <c r="LY58" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ58" t="s">
         <v>209</v>
       </c>
-      <c r="LW58" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX58" t="s">
-        <v>23</v>
-      </c>
-      <c r="LY58" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ58" t="s">
-        <v>58</v>
-      </c>
       <c r="MA58" t="s">
-        <v>59</v>
+        <v>262</v>
       </c>
       <c r="MB58" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="MC58" t="s">
         <v>28</v>
@@ -6907,28 +6907,28 @@
         <v>265</v>
       </c>
       <c r="LU59" t="s">
+        <v>56</v>
+      </c>
+      <c r="LV59" t="s">
         <v>208</v>
       </c>
-      <c r="LV59" t="s">
+      <c r="LW59" t="s">
+        <v>58</v>
+      </c>
+      <c r="LX59" t="s">
+        <v>24</v>
+      </c>
+      <c r="LY59" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ59" t="s">
         <v>209</v>
       </c>
-      <c r="LW59" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX59" t="s">
-        <v>23</v>
-      </c>
-      <c r="LY59" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ59" t="s">
-        <v>58</v>
-      </c>
       <c r="MA59" t="s">
-        <v>59</v>
+        <v>266</v>
       </c>
       <c r="MB59" t="s">
-        <v>266</v>
+        <v>27</v>
       </c>
       <c r="MC59" t="s">
         <v>28</v>
@@ -6948,28 +6948,28 @@
         <v>269</v>
       </c>
       <c r="LU60" t="s">
+        <v>56</v>
+      </c>
+      <c r="LV60" t="s">
         <v>208</v>
       </c>
-      <c r="LV60" t="s">
+      <c r="LW60" t="s">
+        <v>58</v>
+      </c>
+      <c r="LX60" t="s">
+        <v>24</v>
+      </c>
+      <c r="LY60" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ60" t="s">
         <v>209</v>
       </c>
-      <c r="LW60" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX60" t="s">
-        <v>23</v>
-      </c>
-      <c r="LY60" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ60" t="s">
-        <v>58</v>
-      </c>
       <c r="MA60" t="s">
-        <v>59</v>
+        <v>270</v>
       </c>
       <c r="MB60" t="s">
-        <v>270</v>
+        <v>27</v>
       </c>
       <c r="MC60" t="s">
         <v>28</v>
@@ -6989,28 +6989,28 @@
         <v>273</v>
       </c>
       <c r="LU61" t="s">
+        <v>56</v>
+      </c>
+      <c r="LV61" t="s">
         <v>208</v>
       </c>
-      <c r="LV61" t="s">
+      <c r="LW61" t="s">
+        <v>58</v>
+      </c>
+      <c r="LX61" t="s">
+        <v>24</v>
+      </c>
+      <c r="LY61" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ61" t="s">
         <v>209</v>
       </c>
-      <c r="LW61" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX61" t="s">
-        <v>23</v>
-      </c>
-      <c r="LY61" t="s">
-        <v>24</v>
-      </c>
-      <c r="LZ61" t="s">
-        <v>58</v>
-      </c>
       <c r="MA61" t="s">
-        <v>59</v>
+        <v>274</v>
       </c>
       <c r="MB61" t="s">
-        <v>274</v>
+        <v>27</v>
       </c>
       <c r="MC61" t="s">
         <v>28</v>
@@ -7036,13 +7036,13 @@
         <v>279</v>
       </c>
       <c r="LW62" t="s">
-        <v>22</v>
+        <v>280</v>
       </c>
       <c r="LX62" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="LY62" t="s">
-        <v>281</v>
+        <v>25</v>
       </c>
       <c r="LZ62" t="s">
         <v>282</v>
@@ -7077,22 +7077,22 @@
         <v>279</v>
       </c>
       <c r="LW63" t="s">
-        <v>22</v>
+        <v>280</v>
       </c>
       <c r="LX63" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="LY63" t="s">
-        <v>281</v>
+        <v>25</v>
       </c>
       <c r="LZ63" t="s">
         <v>282</v>
       </c>
       <c r="MA63" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="MB63" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="MC63" t="s">
         <v>28</v>
@@ -7118,22 +7118,22 @@
         <v>279</v>
       </c>
       <c r="LW64" t="s">
-        <v>22</v>
+        <v>280</v>
       </c>
       <c r="LX64" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="LY64" t="s">
-        <v>281</v>
+        <v>25</v>
       </c>
       <c r="LZ64" t="s">
         <v>282</v>
       </c>
       <c r="MA64" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="MB64" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="MC64" t="s">
         <v>28</v>
@@ -7159,22 +7159,22 @@
         <v>279</v>
       </c>
       <c r="LW65" t="s">
-        <v>22</v>
+        <v>280</v>
       </c>
       <c r="LX65" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="LY65" t="s">
-        <v>281</v>
+        <v>25</v>
       </c>
       <c r="LZ65" t="s">
         <v>282</v>
       </c>
       <c r="MA65" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="MB65" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="MC65" t="s">
         <v>28</v>
@@ -7200,22 +7200,22 @@
         <v>279</v>
       </c>
       <c r="LW66" t="s">
-        <v>22</v>
+        <v>280</v>
       </c>
       <c r="LX66" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="LY66" t="s">
-        <v>281</v>
+        <v>25</v>
       </c>
       <c r="LZ66" t="s">
         <v>282</v>
       </c>
       <c r="MA66" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="MB66" t="s">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="MC66" t="s">
         <v>28</v>
@@ -7241,22 +7241,22 @@
         <v>279</v>
       </c>
       <c r="LW67" t="s">
-        <v>22</v>
+        <v>280</v>
       </c>
       <c r="LX67" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="LY67" t="s">
-        <v>281</v>
+        <v>25</v>
       </c>
       <c r="LZ67" t="s">
         <v>282</v>
       </c>
       <c r="MA67" t="s">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="MB67" t="s">
-        <v>304</v>
+        <v>284</v>
       </c>
       <c r="MC67" t="s">
         <v>28</v>
@@ -7282,22 +7282,22 @@
         <v>279</v>
       </c>
       <c r="LW68" t="s">
-        <v>22</v>
+        <v>280</v>
       </c>
       <c r="LX68" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="LY68" t="s">
-        <v>281</v>
+        <v>25</v>
       </c>
       <c r="LZ68" t="s">
         <v>282</v>
       </c>
       <c r="MA68" t="s">
-        <v>283</v>
+        <v>308</v>
       </c>
       <c r="MB68" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="MC68" t="s">
         <v>28</v>
@@ -7323,22 +7323,22 @@
         <v>279</v>
       </c>
       <c r="LW69" t="s">
-        <v>22</v>
+        <v>280</v>
       </c>
       <c r="LX69" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="LY69" t="s">
-        <v>281</v>
+        <v>25</v>
       </c>
       <c r="LZ69" t="s">
         <v>282</v>
       </c>
       <c r="MA69" t="s">
-        <v>283</v>
+        <v>312</v>
       </c>
       <c r="MB69" t="s">
-        <v>312</v>
+        <v>284</v>
       </c>
       <c r="MC69" t="s">
         <v>28</v>
@@ -7364,22 +7364,22 @@
         <v>279</v>
       </c>
       <c r="LW70" t="s">
-        <v>22</v>
+        <v>280</v>
       </c>
       <c r="LX70" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="LY70" t="s">
-        <v>281</v>
+        <v>25</v>
       </c>
       <c r="LZ70" t="s">
         <v>282</v>
       </c>
       <c r="MA70" t="s">
-        <v>283</v>
+        <v>316</v>
       </c>
       <c r="MB70" t="s">
-        <v>316</v>
+        <v>284</v>
       </c>
       <c r="MC70" t="s">
         <v>28</v>
@@ -7405,22 +7405,22 @@
         <v>279</v>
       </c>
       <c r="LW71" t="s">
-        <v>22</v>
+        <v>280</v>
       </c>
       <c r="LX71" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="LY71" t="s">
-        <v>281</v>
+        <v>25</v>
       </c>
       <c r="LZ71" t="s">
         <v>282</v>
       </c>
       <c r="MA71" t="s">
-        <v>283</v>
+        <v>320</v>
       </c>
       <c r="MB71" t="s">
-        <v>320</v>
+        <v>284</v>
       </c>
       <c r="MC71" t="s">
         <v>28</v>
@@ -7446,22 +7446,22 @@
         <v>279</v>
       </c>
       <c r="LW72" t="s">
-        <v>22</v>
+        <v>280</v>
       </c>
       <c r="LX72" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="LY72" t="s">
-        <v>281</v>
+        <v>25</v>
       </c>
       <c r="LZ72" t="s">
         <v>282</v>
       </c>
       <c r="MA72" t="s">
-        <v>283</v>
+        <v>324</v>
       </c>
       <c r="MB72" t="s">
-        <v>324</v>
+        <v>284</v>
       </c>
       <c r="MC72" t="s">
         <v>28</v>
@@ -7487,22 +7487,22 @@
         <v>279</v>
       </c>
       <c r="LW73" t="s">
-        <v>22</v>
+        <v>280</v>
       </c>
       <c r="LX73" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="LY73" t="s">
-        <v>281</v>
+        <v>25</v>
       </c>
       <c r="LZ73" t="s">
         <v>282</v>
       </c>
       <c r="MA73" t="s">
-        <v>283</v>
+        <v>328</v>
       </c>
       <c r="MB73" t="s">
-        <v>328</v>
+        <v>284</v>
       </c>
       <c r="MC73" t="s">
         <v>28</v>
@@ -7528,22 +7528,22 @@
         <v>279</v>
       </c>
       <c r="LW74" t="s">
-        <v>22</v>
+        <v>280</v>
       </c>
       <c r="LX74" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="LY74" t="s">
-        <v>281</v>
+        <v>25</v>
       </c>
       <c r="LZ74" t="s">
         <v>282</v>
       </c>
       <c r="MA74" t="s">
-        <v>283</v>
+        <v>332</v>
       </c>
       <c r="MB74" t="s">
-        <v>332</v>
+        <v>284</v>
       </c>
       <c r="MC74" t="s">
         <v>28</v>
@@ -7569,22 +7569,22 @@
         <v>279</v>
       </c>
       <c r="LW75" t="s">
-        <v>22</v>
+        <v>280</v>
       </c>
       <c r="LX75" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="LY75" t="s">
-        <v>281</v>
+        <v>25</v>
       </c>
       <c r="LZ75" t="s">
         <v>282</v>
       </c>
       <c r="MA75" t="s">
-        <v>283</v>
+        <v>336</v>
       </c>
       <c r="MB75" t="s">
-        <v>336</v>
+        <v>284</v>
       </c>
       <c r="MC75" t="s">
         <v>28</v>
@@ -7610,22 +7610,22 @@
         <v>279</v>
       </c>
       <c r="LW76" t="s">
-        <v>22</v>
+        <v>280</v>
       </c>
       <c r="LX76" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="LY76" t="s">
-        <v>281</v>
+        <v>25</v>
       </c>
       <c r="LZ76" t="s">
         <v>282</v>
       </c>
       <c r="MA76" t="s">
-        <v>283</v>
+        <v>340</v>
       </c>
       <c r="MB76" t="s">
-        <v>340</v>
+        <v>284</v>
       </c>
       <c r="MC76" t="s">
         <v>28</v>
@@ -7651,22 +7651,22 @@
         <v>279</v>
       </c>
       <c r="LW77" t="s">
-        <v>22</v>
+        <v>280</v>
       </c>
       <c r="LX77" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="LY77" t="s">
-        <v>281</v>
+        <v>25</v>
       </c>
       <c r="LZ77" t="s">
         <v>282</v>
       </c>
       <c r="MA77" t="s">
-        <v>283</v>
+        <v>344</v>
       </c>
       <c r="MB77" t="s">
-        <v>344</v>
+        <v>284</v>
       </c>
       <c r="MC77" t="s">
         <v>28</v>
@@ -7692,22 +7692,22 @@
         <v>279</v>
       </c>
       <c r="LW78" t="s">
-        <v>22</v>
+        <v>280</v>
       </c>
       <c r="LX78" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="LY78" t="s">
-        <v>281</v>
+        <v>25</v>
       </c>
       <c r="LZ78" t="s">
         <v>282</v>
       </c>
       <c r="MA78" t="s">
-        <v>283</v>
+        <v>348</v>
       </c>
       <c r="MB78" t="s">
-        <v>348</v>
+        <v>284</v>
       </c>
       <c r="MC78" t="s">
         <v>28</v>
@@ -7733,22 +7733,22 @@
         <v>279</v>
       </c>
       <c r="LW79" t="s">
-        <v>22</v>
+        <v>280</v>
       </c>
       <c r="LX79" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="LY79" t="s">
-        <v>281</v>
+        <v>25</v>
       </c>
       <c r="LZ79" t="s">
         <v>282</v>
       </c>
       <c r="MA79" t="s">
-        <v>283</v>
+        <v>352</v>
       </c>
       <c r="MB79" t="s">
-        <v>352</v>
+        <v>284</v>
       </c>
       <c r="MC79" t="s">
         <v>28</v>
@@ -7774,22 +7774,22 @@
         <v>279</v>
       </c>
       <c r="LW80" t="s">
-        <v>22</v>
+        <v>280</v>
       </c>
       <c r="LX80" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="LY80" t="s">
-        <v>281</v>
+        <v>25</v>
       </c>
       <c r="LZ80" t="s">
         <v>282</v>
       </c>
       <c r="MA80" t="s">
-        <v>283</v>
+        <v>356</v>
       </c>
       <c r="MB80" t="s">
-        <v>356</v>
+        <v>284</v>
       </c>
       <c r="MC80" t="s">
         <v>28</v>
@@ -7815,22 +7815,22 @@
         <v>279</v>
       </c>
       <c r="LW81" t="s">
-        <v>22</v>
+        <v>280</v>
       </c>
       <c r="LX81" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="LY81" t="s">
-        <v>281</v>
+        <v>25</v>
       </c>
       <c r="LZ81" t="s">
         <v>282</v>
       </c>
       <c r="MA81" t="s">
-        <v>283</v>
+        <v>360</v>
       </c>
       <c r="MB81" t="s">
-        <v>360</v>
+        <v>284</v>
       </c>
       <c r="MC81" t="s">
         <v>28</v>
@@ -7856,22 +7856,22 @@
         <v>279</v>
       </c>
       <c r="LW82" t="s">
-        <v>22</v>
+        <v>280</v>
       </c>
       <c r="LX82" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="LY82" t="s">
-        <v>281</v>
+        <v>25</v>
       </c>
       <c r="LZ82" t="s">
         <v>282</v>
       </c>
       <c r="MA82" t="s">
-        <v>283</v>
+        <v>364</v>
       </c>
       <c r="MB82" t="s">
-        <v>364</v>
+        <v>284</v>
       </c>
       <c r="MC82" t="s">
         <v>28</v>
@@ -7897,22 +7897,22 @@
         <v>279</v>
       </c>
       <c r="LW83" t="s">
-        <v>22</v>
+        <v>280</v>
       </c>
       <c r="LX83" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="LY83" t="s">
-        <v>281</v>
+        <v>25</v>
       </c>
       <c r="LZ83" t="s">
         <v>282</v>
       </c>
       <c r="MA83" t="s">
-        <v>283</v>
+        <v>368</v>
       </c>
       <c r="MB83" t="s">
-        <v>368</v>
+        <v>284</v>
       </c>
       <c r="MC83" t="s">
         <v>28</v>
@@ -7938,22 +7938,22 @@
         <v>279</v>
       </c>
       <c r="LW84" t="s">
-        <v>22</v>
+        <v>280</v>
       </c>
       <c r="LX84" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="LY84" t="s">
-        <v>281</v>
+        <v>25</v>
       </c>
       <c r="LZ84" t="s">
         <v>282</v>
       </c>
       <c r="MA84" t="s">
-        <v>283</v>
+        <v>372</v>
       </c>
       <c r="MB84" t="s">
-        <v>372</v>
+        <v>284</v>
       </c>
       <c r="MC84" t="s">
         <v>28</v>
@@ -7979,22 +7979,22 @@
         <v>279</v>
       </c>
       <c r="LW85" t="s">
-        <v>22</v>
+        <v>280</v>
       </c>
       <c r="LX85" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="LY85" t="s">
-        <v>281</v>
+        <v>25</v>
       </c>
       <c r="LZ85" t="s">
         <v>282</v>
       </c>
       <c r="MA85" t="s">
-        <v>283</v>
+        <v>376</v>
       </c>
       <c r="MB85" t="s">
-        <v>376</v>
+        <v>284</v>
       </c>
       <c r="MC85" t="s">
         <v>28</v>
@@ -8020,22 +8020,22 @@
         <v>279</v>
       </c>
       <c r="LW86" t="s">
-        <v>22</v>
+        <v>280</v>
       </c>
       <c r="LX86" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="LY86" t="s">
-        <v>281</v>
+        <v>25</v>
       </c>
       <c r="LZ86" t="s">
         <v>282</v>
       </c>
       <c r="MA86" t="s">
-        <v>283</v>
+        <v>380</v>
       </c>
       <c r="MB86" t="s">
-        <v>380</v>
+        <v>284</v>
       </c>
       <c r="MC86" t="s">
         <v>28</v>
@@ -8061,22 +8061,22 @@
         <v>279</v>
       </c>
       <c r="LW87" t="s">
-        <v>22</v>
+        <v>280</v>
       </c>
       <c r="LX87" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="LY87" t="s">
-        <v>281</v>
+        <v>25</v>
       </c>
       <c r="LZ87" t="s">
         <v>282</v>
       </c>
       <c r="MA87" t="s">
-        <v>283</v>
+        <v>384</v>
       </c>
       <c r="MB87" t="s">
-        <v>384</v>
+        <v>284</v>
       </c>
       <c r="MC87" t="s">
         <v>28</v>
@@ -8102,22 +8102,22 @@
         <v>279</v>
       </c>
       <c r="LW88" t="s">
-        <v>22</v>
+        <v>280</v>
       </c>
       <c r="LX88" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="LY88" t="s">
-        <v>281</v>
+        <v>25</v>
       </c>
       <c r="LZ88" t="s">
         <v>282</v>
       </c>
       <c r="MA88" t="s">
-        <v>283</v>
+        <v>388</v>
       </c>
       <c r="MB88" t="s">
-        <v>388</v>
+        <v>284</v>
       </c>
       <c r="MC88" t="s">
         <v>28</v>
@@ -8143,22 +8143,22 @@
         <v>279</v>
       </c>
       <c r="LW89" t="s">
-        <v>22</v>
+        <v>280</v>
       </c>
       <c r="LX89" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="LY89" t="s">
-        <v>281</v>
+        <v>25</v>
       </c>
       <c r="LZ89" t="s">
         <v>282</v>
       </c>
       <c r="MA89" t="s">
-        <v>283</v>
+        <v>392</v>
       </c>
       <c r="MB89" t="s">
-        <v>392</v>
+        <v>284</v>
       </c>
       <c r="MC89" t="s">
         <v>28</v>
@@ -8178,28 +8178,28 @@
         <v>395</v>
       </c>
       <c r="LU90" t="s">
+        <v>278</v>
+      </c>
+      <c r="LV90" t="s">
         <v>396</v>
       </c>
-      <c r="LV90" t="s">
+      <c r="LW90" t="s">
+        <v>280</v>
+      </c>
+      <c r="LX90" t="s">
+        <v>281</v>
+      </c>
+      <c r="LY90" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ90" t="s">
         <v>397</v>
       </c>
-      <c r="LW90" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX90" t="s">
-        <v>280</v>
-      </c>
-      <c r="LY90" t="s">
-        <v>281</v>
-      </c>
-      <c r="LZ90" t="s">
-        <v>282</v>
-      </c>
       <c r="MA90" t="s">
-        <v>283</v>
+        <v>398</v>
       </c>
       <c r="MB90" t="s">
-        <v>398</v>
+        <v>284</v>
       </c>
       <c r="MC90" t="s">
         <v>28</v>
@@ -8219,28 +8219,28 @@
         <v>401</v>
       </c>
       <c r="LU91" t="s">
+        <v>278</v>
+      </c>
+      <c r="LV91" t="s">
         <v>396</v>
       </c>
-      <c r="LV91" t="s">
+      <c r="LW91" t="s">
+        <v>280</v>
+      </c>
+      <c r="LX91" t="s">
+        <v>281</v>
+      </c>
+      <c r="LY91" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ91" t="s">
         <v>397</v>
       </c>
-      <c r="LW91" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX91" t="s">
-        <v>280</v>
-      </c>
-      <c r="LY91" t="s">
-        <v>281</v>
-      </c>
-      <c r="LZ91" t="s">
-        <v>282</v>
-      </c>
       <c r="MA91" t="s">
-        <v>283</v>
+        <v>402</v>
       </c>
       <c r="MB91" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="MC91" t="s">
         <v>28</v>
@@ -8260,28 +8260,28 @@
         <v>405</v>
       </c>
       <c r="LU92" t="s">
+        <v>278</v>
+      </c>
+      <c r="LV92" t="s">
         <v>396</v>
       </c>
-      <c r="LV92" t="s">
+      <c r="LW92" t="s">
+        <v>280</v>
+      </c>
+      <c r="LX92" t="s">
+        <v>281</v>
+      </c>
+      <c r="LY92" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ92" t="s">
         <v>397</v>
       </c>
-      <c r="LW92" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX92" t="s">
-        <v>280</v>
-      </c>
-      <c r="LY92" t="s">
-        <v>281</v>
-      </c>
-      <c r="LZ92" t="s">
-        <v>282</v>
-      </c>
       <c r="MA92" t="s">
-        <v>283</v>
+        <v>406</v>
       </c>
       <c r="MB92" t="s">
-        <v>406</v>
+        <v>284</v>
       </c>
       <c r="MC92" t="s">
         <v>28</v>
@@ -8301,28 +8301,28 @@
         <v>409</v>
       </c>
       <c r="LU93" t="s">
+        <v>278</v>
+      </c>
+      <c r="LV93" t="s">
         <v>396</v>
       </c>
-      <c r="LV93" t="s">
+      <c r="LW93" t="s">
+        <v>280</v>
+      </c>
+      <c r="LX93" t="s">
+        <v>281</v>
+      </c>
+      <c r="LY93" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ93" t="s">
         <v>397</v>
       </c>
-      <c r="LW93" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX93" t="s">
-        <v>280</v>
-      </c>
-      <c r="LY93" t="s">
-        <v>281</v>
-      </c>
-      <c r="LZ93" t="s">
-        <v>282</v>
-      </c>
       <c r="MA93" t="s">
-        <v>283</v>
+        <v>410</v>
       </c>
       <c r="MB93" t="s">
-        <v>410</v>
+        <v>284</v>
       </c>
       <c r="MC93" t="s">
         <v>28</v>
@@ -8342,28 +8342,28 @@
         <v>413</v>
       </c>
       <c r="LU94" t="s">
+        <v>278</v>
+      </c>
+      <c r="LV94" t="s">
         <v>396</v>
       </c>
-      <c r="LV94" t="s">
+      <c r="LW94" t="s">
+        <v>280</v>
+      </c>
+      <c r="LX94" t="s">
+        <v>281</v>
+      </c>
+      <c r="LY94" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ94" t="s">
         <v>397</v>
       </c>
-      <c r="LW94" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX94" t="s">
-        <v>280</v>
-      </c>
-      <c r="LY94" t="s">
-        <v>281</v>
-      </c>
-      <c r="LZ94" t="s">
-        <v>282</v>
-      </c>
       <c r="MA94" t="s">
-        <v>283</v>
+        <v>414</v>
       </c>
       <c r="MB94" t="s">
-        <v>414</v>
+        <v>284</v>
       </c>
       <c r="MC94" t="s">
         <v>28</v>
@@ -8383,28 +8383,28 @@
         <v>417</v>
       </c>
       <c r="LU95" t="s">
+        <v>278</v>
+      </c>
+      <c r="LV95" t="s">
         <v>396</v>
       </c>
-      <c r="LV95" t="s">
+      <c r="LW95" t="s">
+        <v>280</v>
+      </c>
+      <c r="LX95" t="s">
+        <v>281</v>
+      </c>
+      <c r="LY95" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ95" t="s">
         <v>397</v>
       </c>
-      <c r="LW95" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX95" t="s">
-        <v>280</v>
-      </c>
-      <c r="LY95" t="s">
-        <v>281</v>
-      </c>
-      <c r="LZ95" t="s">
-        <v>282</v>
-      </c>
       <c r="MA95" t="s">
-        <v>283</v>
+        <v>418</v>
       </c>
       <c r="MB95" t="s">
-        <v>418</v>
+        <v>284</v>
       </c>
       <c r="MC95" t="s">
         <v>28</v>
@@ -8424,28 +8424,28 @@
         <v>421</v>
       </c>
       <c r="LU96" t="s">
+        <v>278</v>
+      </c>
+      <c r="LV96" t="s">
         <v>396</v>
       </c>
-      <c r="LV96" t="s">
+      <c r="LW96" t="s">
+        <v>280</v>
+      </c>
+      <c r="LX96" t="s">
+        <v>281</v>
+      </c>
+      <c r="LY96" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ96" t="s">
         <v>397</v>
       </c>
-      <c r="LW96" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX96" t="s">
-        <v>280</v>
-      </c>
-      <c r="LY96" t="s">
-        <v>281</v>
-      </c>
-      <c r="LZ96" t="s">
-        <v>282</v>
-      </c>
       <c r="MA96" t="s">
-        <v>283</v>
+        <v>422</v>
       </c>
       <c r="MB96" t="s">
-        <v>422</v>
+        <v>284</v>
       </c>
       <c r="MC96" t="s">
         <v>28</v>
@@ -8465,28 +8465,28 @@
         <v>425</v>
       </c>
       <c r="LU97" t="s">
+        <v>278</v>
+      </c>
+      <c r="LV97" t="s">
         <v>396</v>
       </c>
-      <c r="LV97" t="s">
+      <c r="LW97" t="s">
+        <v>280</v>
+      </c>
+      <c r="LX97" t="s">
+        <v>281</v>
+      </c>
+      <c r="LY97" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ97" t="s">
         <v>397</v>
       </c>
-      <c r="LW97" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX97" t="s">
-        <v>280</v>
-      </c>
-      <c r="LY97" t="s">
-        <v>281</v>
-      </c>
-      <c r="LZ97" t="s">
-        <v>282</v>
-      </c>
       <c r="MA97" t="s">
-        <v>283</v>
+        <v>426</v>
       </c>
       <c r="MB97" t="s">
-        <v>426</v>
+        <v>284</v>
       </c>
       <c r="MC97" t="s">
         <v>28</v>
@@ -8506,28 +8506,28 @@
         <v>429</v>
       </c>
       <c r="LU98" t="s">
+        <v>278</v>
+      </c>
+      <c r="LV98" t="s">
         <v>430</v>
       </c>
-      <c r="LV98" t="s">
+      <c r="LW98" t="s">
+        <v>280</v>
+      </c>
+      <c r="LX98" t="s">
+        <v>281</v>
+      </c>
+      <c r="LY98" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ98" t="s">
         <v>431</v>
       </c>
-      <c r="LW98" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX98" t="s">
-        <v>280</v>
-      </c>
-      <c r="LY98" t="s">
-        <v>281</v>
-      </c>
-      <c r="LZ98" t="s">
-        <v>282</v>
-      </c>
       <c r="MA98" t="s">
-        <v>283</v>
+        <v>432</v>
       </c>
       <c r="MB98" t="s">
-        <v>432</v>
+        <v>284</v>
       </c>
       <c r="MC98" t="s">
         <v>28</v>
@@ -8547,28 +8547,28 @@
         <v>435</v>
       </c>
       <c r="LU99" t="s">
+        <v>278</v>
+      </c>
+      <c r="LV99" t="s">
         <v>430</v>
       </c>
-      <c r="LV99" t="s">
+      <c r="LW99" t="s">
+        <v>280</v>
+      </c>
+      <c r="LX99" t="s">
+        <v>281</v>
+      </c>
+      <c r="LY99" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ99" t="s">
         <v>431</v>
       </c>
-      <c r="LW99" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX99" t="s">
-        <v>280</v>
-      </c>
-      <c r="LY99" t="s">
-        <v>281</v>
-      </c>
-      <c r="LZ99" t="s">
-        <v>282</v>
-      </c>
       <c r="MA99" t="s">
-        <v>283</v>
+        <v>436</v>
       </c>
       <c r="MB99" t="s">
-        <v>436</v>
+        <v>284</v>
       </c>
       <c r="MC99" t="s">
         <v>28</v>
@@ -8588,28 +8588,28 @@
         <v>439</v>
       </c>
       <c r="LU100" t="s">
+        <v>278</v>
+      </c>
+      <c r="LV100" t="s">
         <v>430</v>
       </c>
-      <c r="LV100" t="s">
+      <c r="LW100" t="s">
+        <v>280</v>
+      </c>
+      <c r="LX100" t="s">
+        <v>281</v>
+      </c>
+      <c r="LY100" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ100" t="s">
         <v>431</v>
       </c>
-      <c r="LW100" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX100" t="s">
-        <v>280</v>
-      </c>
-      <c r="LY100" t="s">
-        <v>281</v>
-      </c>
-      <c r="LZ100" t="s">
-        <v>282</v>
-      </c>
       <c r="MA100" t="s">
-        <v>283</v>
+        <v>440</v>
       </c>
       <c r="MB100" t="s">
-        <v>440</v>
+        <v>284</v>
       </c>
       <c r="MC100" t="s">
         <v>28</v>
@@ -8629,28 +8629,28 @@
         <v>443</v>
       </c>
       <c r="LU101" t="s">
+        <v>278</v>
+      </c>
+      <c r="LV101" t="s">
         <v>430</v>
       </c>
-      <c r="LV101" t="s">
+      <c r="LW101" t="s">
+        <v>280</v>
+      </c>
+      <c r="LX101" t="s">
+        <v>281</v>
+      </c>
+      <c r="LY101" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ101" t="s">
         <v>431</v>
       </c>
-      <c r="LW101" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX101" t="s">
-        <v>280</v>
-      </c>
-      <c r="LY101" t="s">
-        <v>281</v>
-      </c>
-      <c r="LZ101" t="s">
-        <v>282</v>
-      </c>
       <c r="MA101" t="s">
-        <v>283</v>
+        <v>444</v>
       </c>
       <c r="MB101" t="s">
-        <v>444</v>
+        <v>284</v>
       </c>
       <c r="MC101" t="s">
         <v>28</v>
@@ -8670,28 +8670,28 @@
         <v>447</v>
       </c>
       <c r="LU102" t="s">
+        <v>278</v>
+      </c>
+      <c r="LV102" t="s">
         <v>430</v>
       </c>
-      <c r="LV102" t="s">
+      <c r="LW102" t="s">
+        <v>280</v>
+      </c>
+      <c r="LX102" t="s">
+        <v>281</v>
+      </c>
+      <c r="LY102" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ102" t="s">
         <v>431</v>
       </c>
-      <c r="LW102" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX102" t="s">
-        <v>280</v>
-      </c>
-      <c r="LY102" t="s">
-        <v>281</v>
-      </c>
-      <c r="LZ102" t="s">
-        <v>282</v>
-      </c>
       <c r="MA102" t="s">
-        <v>283</v>
+        <v>448</v>
       </c>
       <c r="MB102" t="s">
-        <v>448</v>
+        <v>284</v>
       </c>
       <c r="MC102" t="s">
         <v>28</v>
@@ -8711,28 +8711,28 @@
         <v>451</v>
       </c>
       <c r="LU103" t="s">
+        <v>278</v>
+      </c>
+      <c r="LV103" t="s">
         <v>430</v>
       </c>
-      <c r="LV103" t="s">
+      <c r="LW103" t="s">
+        <v>280</v>
+      </c>
+      <c r="LX103" t="s">
+        <v>281</v>
+      </c>
+      <c r="LY103" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ103" t="s">
         <v>431</v>
       </c>
-      <c r="LW103" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX103" t="s">
-        <v>280</v>
-      </c>
-      <c r="LY103" t="s">
-        <v>281</v>
-      </c>
-      <c r="LZ103" t="s">
-        <v>282</v>
-      </c>
       <c r="MA103" t="s">
-        <v>283</v>
+        <v>452</v>
       </c>
       <c r="MB103" t="s">
-        <v>452</v>
+        <v>284</v>
       </c>
       <c r="MC103" t="s">
         <v>28</v>
@@ -8752,28 +8752,28 @@
         <v>455</v>
       </c>
       <c r="LU104" t="s">
+        <v>278</v>
+      </c>
+      <c r="LV104" t="s">
         <v>430</v>
       </c>
-      <c r="LV104" t="s">
+      <c r="LW104" t="s">
+        <v>280</v>
+      </c>
+      <c r="LX104" t="s">
+        <v>281</v>
+      </c>
+      <c r="LY104" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ104" t="s">
         <v>431</v>
       </c>
-      <c r="LW104" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX104" t="s">
-        <v>280</v>
-      </c>
-      <c r="LY104" t="s">
-        <v>281</v>
-      </c>
-      <c r="LZ104" t="s">
-        <v>282</v>
-      </c>
       <c r="MA104" t="s">
-        <v>283</v>
+        <v>456</v>
       </c>
       <c r="MB104" t="s">
-        <v>456</v>
+        <v>284</v>
       </c>
       <c r="MC104" t="s">
         <v>28</v>
@@ -8793,28 +8793,28 @@
         <v>459</v>
       </c>
       <c r="LU105" t="s">
+        <v>278</v>
+      </c>
+      <c r="LV105" t="s">
         <v>430</v>
       </c>
-      <c r="LV105" t="s">
+      <c r="LW105" t="s">
+        <v>280</v>
+      </c>
+      <c r="LX105" t="s">
+        <v>281</v>
+      </c>
+      <c r="LY105" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ105" t="s">
         <v>431</v>
       </c>
-      <c r="LW105" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX105" t="s">
-        <v>280</v>
-      </c>
-      <c r="LY105" t="s">
-        <v>281</v>
-      </c>
-      <c r="LZ105" t="s">
-        <v>282</v>
-      </c>
       <c r="MA105" t="s">
-        <v>283</v>
+        <v>460</v>
       </c>
       <c r="MB105" t="s">
-        <v>460</v>
+        <v>284</v>
       </c>
       <c r="MC105" t="s">
         <v>28</v>
@@ -8834,28 +8834,28 @@
         <v>463</v>
       </c>
       <c r="LU106" t="s">
+        <v>278</v>
+      </c>
+      <c r="LV106" t="s">
         <v>430</v>
       </c>
-      <c r="LV106" t="s">
+      <c r="LW106" t="s">
+        <v>280</v>
+      </c>
+      <c r="LX106" t="s">
+        <v>281</v>
+      </c>
+      <c r="LY106" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ106" t="s">
         <v>431</v>
       </c>
-      <c r="LW106" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX106" t="s">
-        <v>280</v>
-      </c>
-      <c r="LY106" t="s">
-        <v>281</v>
-      </c>
-      <c r="LZ106" t="s">
-        <v>282</v>
-      </c>
       <c r="MA106" t="s">
-        <v>283</v>
+        <v>464</v>
       </c>
       <c r="MB106" t="s">
-        <v>464</v>
+        <v>284</v>
       </c>
       <c r="MC106" t="s">
         <v>28</v>
@@ -8875,28 +8875,28 @@
         <v>467</v>
       </c>
       <c r="LU107" t="s">
+        <v>278</v>
+      </c>
+      <c r="LV107" t="s">
         <v>430</v>
       </c>
-      <c r="LV107" t="s">
+      <c r="LW107" t="s">
+        <v>280</v>
+      </c>
+      <c r="LX107" t="s">
+        <v>281</v>
+      </c>
+      <c r="LY107" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ107" t="s">
         <v>431</v>
       </c>
-      <c r="LW107" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX107" t="s">
-        <v>280</v>
-      </c>
-      <c r="LY107" t="s">
-        <v>281</v>
-      </c>
-      <c r="LZ107" t="s">
-        <v>282</v>
-      </c>
       <c r="MA107" t="s">
-        <v>283</v>
+        <v>468</v>
       </c>
       <c r="MB107" t="s">
-        <v>468</v>
+        <v>284</v>
       </c>
       <c r="MC107" t="s">
         <v>28</v>
@@ -8916,28 +8916,28 @@
         <v>471</v>
       </c>
       <c r="LU108" t="s">
+        <v>278</v>
+      </c>
+      <c r="LV108" t="s">
         <v>430</v>
       </c>
-      <c r="LV108" t="s">
+      <c r="LW108" t="s">
+        <v>280</v>
+      </c>
+      <c r="LX108" t="s">
+        <v>281</v>
+      </c>
+      <c r="LY108" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ108" t="s">
         <v>431</v>
       </c>
-      <c r="LW108" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX108" t="s">
-        <v>280</v>
-      </c>
-      <c r="LY108" t="s">
-        <v>281</v>
-      </c>
-      <c r="LZ108" t="s">
-        <v>282</v>
-      </c>
       <c r="MA108" t="s">
-        <v>283</v>
+        <v>472</v>
       </c>
       <c r="MB108" t="s">
-        <v>472</v>
+        <v>284</v>
       </c>
       <c r="MC108" t="s">
         <v>28</v>
@@ -8957,28 +8957,28 @@
         <v>475</v>
       </c>
       <c r="LU109" t="s">
+        <v>278</v>
+      </c>
+      <c r="LV109" t="s">
         <v>430</v>
       </c>
-      <c r="LV109" t="s">
+      <c r="LW109" t="s">
+        <v>280</v>
+      </c>
+      <c r="LX109" t="s">
+        <v>281</v>
+      </c>
+      <c r="LY109" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ109" t="s">
         <v>431</v>
       </c>
-      <c r="LW109" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX109" t="s">
-        <v>280</v>
-      </c>
-      <c r="LY109" t="s">
-        <v>281</v>
-      </c>
-      <c r="LZ109" t="s">
-        <v>282</v>
-      </c>
       <c r="MA109" t="s">
-        <v>283</v>
+        <v>476</v>
       </c>
       <c r="MB109" t="s">
-        <v>476</v>
+        <v>284</v>
       </c>
       <c r="MC109" t="s">
         <v>28</v>
@@ -8998,28 +8998,28 @@
         <v>479</v>
       </c>
       <c r="LU110" t="s">
+        <v>278</v>
+      </c>
+      <c r="LV110" t="s">
         <v>430</v>
       </c>
-      <c r="LV110" t="s">
+      <c r="LW110" t="s">
+        <v>280</v>
+      </c>
+      <c r="LX110" t="s">
+        <v>281</v>
+      </c>
+      <c r="LY110" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ110" t="s">
         <v>431</v>
       </c>
-      <c r="LW110" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX110" t="s">
-        <v>280</v>
-      </c>
-      <c r="LY110" t="s">
-        <v>281</v>
-      </c>
-      <c r="LZ110" t="s">
-        <v>282</v>
-      </c>
       <c r="MA110" t="s">
-        <v>283</v>
+        <v>480</v>
       </c>
       <c r="MB110" t="s">
-        <v>480</v>
+        <v>284</v>
       </c>
       <c r="MC110" t="s">
         <v>28</v>
@@ -9039,28 +9039,28 @@
         <v>483</v>
       </c>
       <c r="LU111" t="s">
+        <v>278</v>
+      </c>
+      <c r="LV111" t="s">
         <v>430</v>
       </c>
-      <c r="LV111" t="s">
+      <c r="LW111" t="s">
+        <v>280</v>
+      </c>
+      <c r="LX111" t="s">
+        <v>281</v>
+      </c>
+      <c r="LY111" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ111" t="s">
         <v>431</v>
       </c>
-      <c r="LW111" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX111" t="s">
-        <v>280</v>
-      </c>
-      <c r="LY111" t="s">
-        <v>281</v>
-      </c>
-      <c r="LZ111" t="s">
-        <v>282</v>
-      </c>
       <c r="MA111" t="s">
-        <v>283</v>
+        <v>484</v>
       </c>
       <c r="MB111" t="s">
-        <v>484</v>
+        <v>284</v>
       </c>
       <c r="MC111" t="s">
         <v>28</v>
@@ -9080,28 +9080,28 @@
         <v>487</v>
       </c>
       <c r="LU112" t="s">
+        <v>278</v>
+      </c>
+      <c r="LV112" t="s">
         <v>430</v>
       </c>
-      <c r="LV112" t="s">
+      <c r="LW112" t="s">
+        <v>280</v>
+      </c>
+      <c r="LX112" t="s">
+        <v>281</v>
+      </c>
+      <c r="LY112" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ112" t="s">
         <v>431</v>
       </c>
-      <c r="LW112" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX112" t="s">
-        <v>280</v>
-      </c>
-      <c r="LY112" t="s">
-        <v>281</v>
-      </c>
-      <c r="LZ112" t="s">
-        <v>282</v>
-      </c>
       <c r="MA112" t="s">
-        <v>283</v>
+        <v>488</v>
       </c>
       <c r="MB112" t="s">
-        <v>488</v>
+        <v>284</v>
       </c>
       <c r="MC112" t="s">
         <v>28</v>
@@ -9121,28 +9121,28 @@
         <v>491</v>
       </c>
       <c r="LU113" t="s">
+        <v>278</v>
+      </c>
+      <c r="LV113" t="s">
         <v>430</v>
       </c>
-      <c r="LV113" t="s">
+      <c r="LW113" t="s">
+        <v>280</v>
+      </c>
+      <c r="LX113" t="s">
+        <v>281</v>
+      </c>
+      <c r="LY113" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ113" t="s">
         <v>431</v>
       </c>
-      <c r="LW113" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX113" t="s">
-        <v>280</v>
-      </c>
-      <c r="LY113" t="s">
-        <v>281</v>
-      </c>
-      <c r="LZ113" t="s">
-        <v>282</v>
-      </c>
       <c r="MA113" t="s">
-        <v>283</v>
+        <v>492</v>
       </c>
       <c r="MB113" t="s">
-        <v>492</v>
+        <v>284</v>
       </c>
       <c r="MC113" t="s">
         <v>28</v>
@@ -9161,23 +9161,23 @@
       <c r="LT114" t="s">
         <v>495</v>
       </c>
+      <c r="LU114" t="s">
+        <v>496</v>
+      </c>
       <c r="LW114" t="s">
-        <v>22</v>
+        <v>497</v>
       </c>
       <c r="LX114" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="LY114" t="s">
-        <v>281</v>
-      </c>
-      <c r="LZ114" t="s">
-        <v>496</v>
+        <v>25</v>
       </c>
       <c r="MA114" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="MB114" t="s">
-        <v>498</v>
+        <v>284</v>
       </c>
       <c r="MC114" t="s">
         <v>28</v>
@@ -9196,23 +9196,23 @@
       <c r="LT115" t="s">
         <v>501</v>
       </c>
+      <c r="LU115" t="s">
+        <v>496</v>
+      </c>
       <c r="LW115" t="s">
-        <v>22</v>
+        <v>497</v>
       </c>
       <c r="LX115" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="LY115" t="s">
-        <v>281</v>
-      </c>
-      <c r="LZ115" t="s">
-        <v>496</v>
+        <v>25</v>
       </c>
       <c r="MA115" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="MB115" t="s">
-        <v>502</v>
+        <v>284</v>
       </c>
       <c r="MC115" t="s">
         <v>28</v>
@@ -9231,23 +9231,23 @@
       <c r="LT116" t="s">
         <v>505</v>
       </c>
+      <c r="LU116" t="s">
+        <v>496</v>
+      </c>
       <c r="LW116" t="s">
-        <v>22</v>
+        <v>497</v>
       </c>
       <c r="LX116" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="LY116" t="s">
-        <v>281</v>
-      </c>
-      <c r="LZ116" t="s">
-        <v>496</v>
+        <v>25</v>
       </c>
       <c r="MA116" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="MB116" t="s">
-        <v>506</v>
+        <v>284</v>
       </c>
       <c r="MC116" t="s">
         <v>28</v>
@@ -9266,23 +9266,23 @@
       <c r="LT117" t="s">
         <v>509</v>
       </c>
+      <c r="LU117" t="s">
+        <v>496</v>
+      </c>
       <c r="LW117" t="s">
-        <v>22</v>
+        <v>497</v>
       </c>
       <c r="LX117" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="LY117" t="s">
-        <v>281</v>
-      </c>
-      <c r="LZ117" t="s">
-        <v>496</v>
+        <v>25</v>
       </c>
       <c r="MA117" t="s">
-        <v>497</v>
+        <v>510</v>
       </c>
       <c r="MB117" t="s">
-        <v>510</v>
+        <v>284</v>
       </c>
       <c r="MC117" t="s">
         <v>28</v>
@@ -9301,23 +9301,23 @@
       <c r="LT118" t="s">
         <v>513</v>
       </c>
+      <c r="LU118" t="s">
+        <v>496</v>
+      </c>
       <c r="LW118" t="s">
-        <v>22</v>
+        <v>497</v>
       </c>
       <c r="LX118" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="LY118" t="s">
-        <v>281</v>
-      </c>
-      <c r="LZ118" t="s">
-        <v>496</v>
+        <v>25</v>
       </c>
       <c r="MA118" t="s">
-        <v>497</v>
+        <v>514</v>
       </c>
       <c r="MB118" t="s">
-        <v>514</v>
+        <v>284</v>
       </c>
       <c r="MC118" t="s">
         <v>28</v>
@@ -9336,10 +9336,10 @@
       <c r="LT119" t="s">
         <v>517</v>
       </c>
-      <c r="LW119" t="s">
-        <v>22</v>
-      </c>
-      <c r="MB119" t="s">
+      <c r="LY119" t="s">
+        <v>25</v>
+      </c>
+      <c r="MA119" t="s">
         <v>518</v>
       </c>
       <c r="MC119" t="s">
@@ -9359,17 +9359,17 @@
       <c r="LT120" t="s">
         <v>521</v>
       </c>
+      <c r="LU120" t="s">
+        <v>522</v>
+      </c>
       <c r="LW120" t="s">
-        <v>22</v>
+        <v>523</v>
       </c>
       <c r="LX120" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY120" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ120" t="s">
-        <v>524</v>
+        <v>25</v>
       </c>
       <c r="MA120" t="s">
         <v>525</v>
@@ -9394,23 +9394,23 @@
       <c r="LT121" t="s">
         <v>529</v>
       </c>
+      <c r="LU121" t="s">
+        <v>522</v>
+      </c>
       <c r="LW121" t="s">
-        <v>22</v>
+        <v>523</v>
       </c>
       <c r="LX121" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY121" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ121" t="s">
-        <v>524</v>
+        <v>25</v>
       </c>
       <c r="MA121" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="MB121" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="MC121" t="s">
         <v>28</v>
@@ -9429,23 +9429,23 @@
       <c r="LT122" t="s">
         <v>533</v>
       </c>
+      <c r="LU122" t="s">
+        <v>522</v>
+      </c>
       <c r="LW122" t="s">
-        <v>22</v>
+        <v>523</v>
       </c>
       <c r="LX122" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY122" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ122" t="s">
-        <v>524</v>
+        <v>25</v>
       </c>
       <c r="MA122" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="MB122" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="MC122" t="s">
         <v>28</v>
@@ -9464,23 +9464,23 @@
       <c r="LT123" t="s">
         <v>537</v>
       </c>
+      <c r="LU123" t="s">
+        <v>522</v>
+      </c>
       <c r="LW123" t="s">
-        <v>22</v>
+        <v>523</v>
       </c>
       <c r="LX123" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY123" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ123" t="s">
-        <v>524</v>
+        <v>25</v>
       </c>
       <c r="MA123" t="s">
-        <v>525</v>
+        <v>538</v>
       </c>
       <c r="MB123" t="s">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="MC123" t="s">
         <v>28</v>
@@ -9499,23 +9499,23 @@
       <c r="LT124" t="s">
         <v>541</v>
       </c>
+      <c r="LU124" t="s">
+        <v>522</v>
+      </c>
       <c r="LW124" t="s">
-        <v>22</v>
+        <v>523</v>
       </c>
       <c r="LX124" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY124" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ124" t="s">
-        <v>524</v>
+        <v>25</v>
       </c>
       <c r="MA124" t="s">
-        <v>525</v>
+        <v>542</v>
       </c>
       <c r="MB124" t="s">
-        <v>542</v>
+        <v>526</v>
       </c>
       <c r="MC124" t="s">
         <v>28</v>
@@ -9534,23 +9534,23 @@
       <c r="LT125" t="s">
         <v>545</v>
       </c>
+      <c r="LU125" t="s">
+        <v>546</v>
+      </c>
       <c r="LW125" t="s">
-        <v>22</v>
+        <v>547</v>
       </c>
       <c r="LX125" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY125" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ125" t="s">
-        <v>546</v>
+        <v>25</v>
       </c>
       <c r="MA125" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="MB125" t="s">
-        <v>548</v>
+        <v>526</v>
       </c>
       <c r="MC125" t="s">
         <v>28</v>
@@ -9569,23 +9569,23 @@
       <c r="LT126" t="s">
         <v>551</v>
       </c>
+      <c r="LU126" t="s">
+        <v>546</v>
+      </c>
       <c r="LW126" t="s">
-        <v>22</v>
+        <v>547</v>
       </c>
       <c r="LX126" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY126" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ126" t="s">
-        <v>546</v>
+        <v>25</v>
       </c>
       <c r="MA126" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="MB126" t="s">
-        <v>552</v>
+        <v>526</v>
       </c>
       <c r="MC126" t="s">
         <v>28</v>
@@ -9604,23 +9604,23 @@
       <c r="LT127" t="s">
         <v>555</v>
       </c>
+      <c r="LU127" t="s">
+        <v>546</v>
+      </c>
       <c r="LW127" t="s">
-        <v>22</v>
+        <v>547</v>
       </c>
       <c r="LX127" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY127" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ127" t="s">
-        <v>546</v>
+        <v>25</v>
       </c>
       <c r="MA127" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="MB127" t="s">
-        <v>556</v>
+        <v>526</v>
       </c>
       <c r="MC127" t="s">
         <v>28</v>
@@ -9639,23 +9639,23 @@
       <c r="LT128" t="s">
         <v>559</v>
       </c>
+      <c r="LU128" t="s">
+        <v>546</v>
+      </c>
       <c r="LW128" t="s">
-        <v>22</v>
+        <v>547</v>
       </c>
       <c r="LX128" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY128" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ128" t="s">
-        <v>546</v>
+        <v>25</v>
       </c>
       <c r="MA128" t="s">
-        <v>547</v>
+        <v>560</v>
       </c>
       <c r="MB128" t="s">
-        <v>560</v>
+        <v>526</v>
       </c>
       <c r="MC128" t="s">
         <v>28</v>
@@ -9674,23 +9674,23 @@
       <c r="LT129" t="s">
         <v>563</v>
       </c>
+      <c r="LU129" t="s">
+        <v>546</v>
+      </c>
       <c r="LW129" t="s">
-        <v>22</v>
+        <v>547</v>
       </c>
       <c r="LX129" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY129" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ129" t="s">
-        <v>546</v>
+        <v>25</v>
       </c>
       <c r="MA129" t="s">
-        <v>547</v>
+        <v>564</v>
       </c>
       <c r="MB129" t="s">
-        <v>564</v>
+        <v>526</v>
       </c>
       <c r="MC129" t="s">
         <v>28</v>
@@ -9709,23 +9709,23 @@
       <c r="LT130" t="s">
         <v>567</v>
       </c>
+      <c r="LU130" t="s">
+        <v>546</v>
+      </c>
       <c r="LW130" t="s">
-        <v>22</v>
+        <v>547</v>
       </c>
       <c r="LX130" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY130" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ130" t="s">
-        <v>546</v>
+        <v>25</v>
       </c>
       <c r="MA130" t="s">
-        <v>547</v>
+        <v>568</v>
       </c>
       <c r="MB130" t="s">
-        <v>568</v>
+        <v>526</v>
       </c>
       <c r="MC130" t="s">
         <v>28</v>
@@ -9744,23 +9744,23 @@
       <c r="LT131" t="s">
         <v>571</v>
       </c>
+      <c r="LU131" t="s">
+        <v>546</v>
+      </c>
       <c r="LW131" t="s">
-        <v>22</v>
+        <v>547</v>
       </c>
       <c r="LX131" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY131" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ131" t="s">
-        <v>546</v>
+        <v>25</v>
       </c>
       <c r="MA131" t="s">
-        <v>547</v>
+        <v>572</v>
       </c>
       <c r="MB131" t="s">
-        <v>572</v>
+        <v>526</v>
       </c>
       <c r="MC131" t="s">
         <v>28</v>
@@ -9779,23 +9779,23 @@
       <c r="LT132" t="s">
         <v>575</v>
       </c>
+      <c r="LU132" t="s">
+        <v>576</v>
+      </c>
       <c r="LW132" t="s">
-        <v>22</v>
+        <v>577</v>
       </c>
       <c r="LX132" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY132" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ132" t="s">
-        <v>576</v>
+        <v>25</v>
       </c>
       <c r="MA132" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="MB132" t="s">
-        <v>578</v>
+        <v>526</v>
       </c>
       <c r="MC132" t="s">
         <v>28</v>
@@ -9814,23 +9814,23 @@
       <c r="LT133" t="s">
         <v>581</v>
       </c>
+      <c r="LU133" t="s">
+        <v>576</v>
+      </c>
       <c r="LW133" t="s">
-        <v>22</v>
+        <v>577</v>
       </c>
       <c r="LX133" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY133" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ133" t="s">
-        <v>576</v>
+        <v>25</v>
       </c>
       <c r="MA133" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="MB133" t="s">
-        <v>582</v>
+        <v>526</v>
       </c>
       <c r="MC133" t="s">
         <v>28</v>
@@ -9849,23 +9849,23 @@
       <c r="LT134" t="s">
         <v>585</v>
       </c>
+      <c r="LU134" t="s">
+        <v>576</v>
+      </c>
       <c r="LW134" t="s">
-        <v>22</v>
+        <v>577</v>
       </c>
       <c r="LX134" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY134" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ134" t="s">
-        <v>576</v>
+        <v>25</v>
       </c>
       <c r="MA134" t="s">
-        <v>577</v>
+        <v>586</v>
       </c>
       <c r="MB134" t="s">
-        <v>586</v>
+        <v>526</v>
       </c>
       <c r="MC134" t="s">
         <v>28</v>
@@ -9884,23 +9884,23 @@
       <c r="LT135" t="s">
         <v>589</v>
       </c>
+      <c r="LU135" t="s">
+        <v>576</v>
+      </c>
       <c r="LW135" t="s">
-        <v>22</v>
+        <v>577</v>
       </c>
       <c r="LX135" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY135" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ135" t="s">
-        <v>576</v>
+        <v>25</v>
       </c>
       <c r="MA135" t="s">
-        <v>577</v>
+        <v>590</v>
       </c>
       <c r="MB135" t="s">
-        <v>590</v>
+        <v>526</v>
       </c>
       <c r="MC135" t="s">
         <v>28</v>
@@ -9919,23 +9919,23 @@
       <c r="LT136" t="s">
         <v>593</v>
       </c>
+      <c r="LU136" t="s">
+        <v>576</v>
+      </c>
       <c r="LW136" t="s">
-        <v>22</v>
+        <v>577</v>
       </c>
       <c r="LX136" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY136" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ136" t="s">
-        <v>576</v>
+        <v>25</v>
       </c>
       <c r="MA136" t="s">
-        <v>577</v>
+        <v>594</v>
       </c>
       <c r="MB136" t="s">
-        <v>594</v>
+        <v>526</v>
       </c>
       <c r="MC136" t="s">
         <v>28</v>
@@ -9954,23 +9954,23 @@
       <c r="LT137" t="s">
         <v>597</v>
       </c>
+      <c r="LU137" t="s">
+        <v>576</v>
+      </c>
       <c r="LW137" t="s">
-        <v>22</v>
+        <v>577</v>
       </c>
       <c r="LX137" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY137" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ137" t="s">
-        <v>576</v>
+        <v>25</v>
       </c>
       <c r="MA137" t="s">
-        <v>577</v>
+        <v>598</v>
       </c>
       <c r="MB137" t="s">
-        <v>598</v>
+        <v>526</v>
       </c>
       <c r="MC137" t="s">
         <v>28</v>
@@ -9989,23 +9989,23 @@
       <c r="LT138" t="s">
         <v>601</v>
       </c>
+      <c r="LU138" t="s">
+        <v>576</v>
+      </c>
       <c r="LW138" t="s">
-        <v>22</v>
+        <v>577</v>
       </c>
       <c r="LX138" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY138" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ138" t="s">
-        <v>576</v>
+        <v>25</v>
       </c>
       <c r="MA138" t="s">
-        <v>577</v>
+        <v>602</v>
       </c>
       <c r="MB138" t="s">
-        <v>602</v>
+        <v>526</v>
       </c>
       <c r="MC138" t="s">
         <v>28</v>
@@ -10024,23 +10024,23 @@
       <c r="LT139" t="s">
         <v>605</v>
       </c>
+      <c r="LU139" t="s">
+        <v>576</v>
+      </c>
       <c r="LW139" t="s">
-        <v>22</v>
+        <v>577</v>
       </c>
       <c r="LX139" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY139" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ139" t="s">
-        <v>576</v>
+        <v>25</v>
       </c>
       <c r="MA139" t="s">
-        <v>577</v>
+        <v>606</v>
       </c>
       <c r="MB139" t="s">
-        <v>606</v>
+        <v>526</v>
       </c>
       <c r="MC139" t="s">
         <v>28</v>
@@ -10059,23 +10059,23 @@
       <c r="LT140" t="s">
         <v>609</v>
       </c>
+      <c r="LU140" t="s">
+        <v>576</v>
+      </c>
       <c r="LW140" t="s">
-        <v>22</v>
+        <v>577</v>
       </c>
       <c r="LX140" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY140" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ140" t="s">
-        <v>576</v>
+        <v>25</v>
       </c>
       <c r="MA140" t="s">
-        <v>577</v>
+        <v>610</v>
       </c>
       <c r="MB140" t="s">
-        <v>610</v>
+        <v>526</v>
       </c>
       <c r="MC140" t="s">
         <v>28</v>
@@ -10094,23 +10094,23 @@
       <c r="LT141" t="s">
         <v>613</v>
       </c>
+      <c r="LU141" t="s">
+        <v>576</v>
+      </c>
       <c r="LW141" t="s">
-        <v>22</v>
+        <v>577</v>
       </c>
       <c r="LX141" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY141" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ141" t="s">
-        <v>576</v>
+        <v>25</v>
       </c>
       <c r="MA141" t="s">
-        <v>577</v>
+        <v>614</v>
       </c>
       <c r="MB141" t="s">
-        <v>614</v>
+        <v>526</v>
       </c>
       <c r="MC141" t="s">
         <v>28</v>
@@ -10129,23 +10129,23 @@
       <c r="LT142" t="s">
         <v>617</v>
       </c>
+      <c r="LU142" t="s">
+        <v>576</v>
+      </c>
       <c r="LW142" t="s">
-        <v>22</v>
+        <v>577</v>
       </c>
       <c r="LX142" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY142" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ142" t="s">
-        <v>576</v>
+        <v>25</v>
       </c>
       <c r="MA142" t="s">
-        <v>577</v>
+        <v>618</v>
       </c>
       <c r="MB142" t="s">
-        <v>618</v>
+        <v>526</v>
       </c>
       <c r="MC142" t="s">
         <v>28</v>
@@ -10164,23 +10164,23 @@
       <c r="LT143" t="s">
         <v>621</v>
       </c>
+      <c r="LU143" t="s">
+        <v>622</v>
+      </c>
       <c r="LW143" t="s">
-        <v>22</v>
+        <v>623</v>
       </c>
       <c r="LX143" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY143" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ143" t="s">
-        <v>622</v>
+        <v>25</v>
       </c>
       <c r="MA143" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="MB143" t="s">
-        <v>624</v>
+        <v>526</v>
       </c>
       <c r="MC143" t="s">
         <v>28</v>
@@ -10199,23 +10199,23 @@
       <c r="LT144" t="s">
         <v>627</v>
       </c>
+      <c r="LU144" t="s">
+        <v>622</v>
+      </c>
       <c r="LW144" t="s">
-        <v>22</v>
+        <v>623</v>
       </c>
       <c r="LX144" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY144" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ144" t="s">
-        <v>622</v>
+        <v>25</v>
       </c>
       <c r="MA144" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="MB144" t="s">
-        <v>628</v>
+        <v>526</v>
       </c>
       <c r="MC144" t="s">
         <v>28</v>
@@ -10234,23 +10234,23 @@
       <c r="LT145" t="s">
         <v>631</v>
       </c>
+      <c r="LU145" t="s">
+        <v>622</v>
+      </c>
       <c r="LW145" t="s">
-        <v>22</v>
+        <v>623</v>
       </c>
       <c r="LX145" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY145" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ145" t="s">
-        <v>622</v>
+        <v>25</v>
       </c>
       <c r="MA145" t="s">
-        <v>623</v>
+        <v>632</v>
       </c>
       <c r="MB145" t="s">
-        <v>632</v>
+        <v>526</v>
       </c>
       <c r="MC145" t="s">
         <v>28</v>
@@ -10269,23 +10269,23 @@
       <c r="LT146" t="s">
         <v>635</v>
       </c>
+      <c r="LU146" t="s">
+        <v>622</v>
+      </c>
       <c r="LW146" t="s">
-        <v>22</v>
+        <v>623</v>
       </c>
       <c r="LX146" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY146" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ146" t="s">
-        <v>622</v>
+        <v>25</v>
       </c>
       <c r="MA146" t="s">
-        <v>623</v>
+        <v>636</v>
       </c>
       <c r="MB146" t="s">
-        <v>636</v>
+        <v>526</v>
       </c>
       <c r="MC146" t="s">
         <v>28</v>
@@ -10304,23 +10304,23 @@
       <c r="LT147" t="s">
         <v>639</v>
       </c>
+      <c r="LU147" t="s">
+        <v>622</v>
+      </c>
       <c r="LW147" t="s">
-        <v>22</v>
+        <v>623</v>
       </c>
       <c r="LX147" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY147" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ147" t="s">
-        <v>622</v>
+        <v>25</v>
       </c>
       <c r="MA147" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
       <c r="MB147" t="s">
-        <v>640</v>
+        <v>526</v>
       </c>
       <c r="MC147" t="s">
         <v>28</v>
@@ -10339,23 +10339,23 @@
       <c r="LT148" t="s">
         <v>643</v>
       </c>
+      <c r="LU148" t="s">
+        <v>622</v>
+      </c>
       <c r="LW148" t="s">
-        <v>22</v>
+        <v>623</v>
       </c>
       <c r="LX148" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY148" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ148" t="s">
-        <v>622</v>
+        <v>25</v>
       </c>
       <c r="MA148" t="s">
-        <v>623</v>
+        <v>644</v>
       </c>
       <c r="MB148" t="s">
-        <v>644</v>
+        <v>526</v>
       </c>
       <c r="MC148" t="s">
         <v>28</v>
@@ -10374,23 +10374,23 @@
       <c r="LT149" t="s">
         <v>647</v>
       </c>
+      <c r="LU149" t="s">
+        <v>622</v>
+      </c>
       <c r="LW149" t="s">
-        <v>22</v>
+        <v>623</v>
       </c>
       <c r="LX149" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY149" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ149" t="s">
-        <v>622</v>
+        <v>25</v>
       </c>
       <c r="MA149" t="s">
-        <v>623</v>
+        <v>648</v>
       </c>
       <c r="MB149" t="s">
-        <v>648</v>
+        <v>526</v>
       </c>
       <c r="MC149" t="s">
         <v>28</v>
@@ -10409,23 +10409,23 @@
       <c r="LT150" t="s">
         <v>651</v>
       </c>
+      <c r="LU150" t="s">
+        <v>622</v>
+      </c>
       <c r="LW150" t="s">
-        <v>22</v>
+        <v>623</v>
       </c>
       <c r="LX150" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY150" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ150" t="s">
-        <v>622</v>
+        <v>25</v>
       </c>
       <c r="MA150" t="s">
-        <v>623</v>
+        <v>652</v>
       </c>
       <c r="MB150" t="s">
-        <v>652</v>
+        <v>526</v>
       </c>
       <c r="MC150" t="s">
         <v>28</v>
@@ -10444,23 +10444,23 @@
       <c r="LT151" t="s">
         <v>655</v>
       </c>
+      <c r="LU151" t="s">
+        <v>622</v>
+      </c>
       <c r="LW151" t="s">
-        <v>22</v>
+        <v>623</v>
       </c>
       <c r="LX151" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY151" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ151" t="s">
-        <v>622</v>
+        <v>25</v>
       </c>
       <c r="MA151" t="s">
-        <v>623</v>
+        <v>656</v>
       </c>
       <c r="MB151" t="s">
-        <v>656</v>
+        <v>526</v>
       </c>
       <c r="MC151" t="s">
         <v>28</v>
@@ -10479,23 +10479,23 @@
       <c r="LT152" t="s">
         <v>659</v>
       </c>
+      <c r="LU152" t="s">
+        <v>660</v>
+      </c>
       <c r="LW152" t="s">
-        <v>22</v>
+        <v>661</v>
       </c>
       <c r="LX152" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY152" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ152" t="s">
-        <v>660</v>
+        <v>25</v>
       </c>
       <c r="MA152" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="MB152" t="s">
-        <v>662</v>
+        <v>526</v>
       </c>
       <c r="MC152" t="s">
         <v>28</v>
@@ -10514,23 +10514,23 @@
       <c r="LT153" t="s">
         <v>665</v>
       </c>
+      <c r="LU153" t="s">
+        <v>660</v>
+      </c>
       <c r="LW153" t="s">
-        <v>22</v>
+        <v>661</v>
       </c>
       <c r="LX153" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY153" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ153" t="s">
-        <v>660</v>
+        <v>25</v>
       </c>
       <c r="MA153" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="MB153" t="s">
-        <v>666</v>
+        <v>526</v>
       </c>
       <c r="MC153" t="s">
         <v>28</v>
@@ -10549,23 +10549,23 @@
       <c r="LT154" t="s">
         <v>669</v>
       </c>
+      <c r="LU154" t="s">
+        <v>660</v>
+      </c>
       <c r="LW154" t="s">
-        <v>22</v>
+        <v>661</v>
       </c>
       <c r="LX154" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY154" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ154" t="s">
-        <v>660</v>
+        <v>25</v>
       </c>
       <c r="MA154" t="s">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="MB154" t="s">
-        <v>670</v>
+        <v>526</v>
       </c>
       <c r="MC154" t="s">
         <v>28</v>
@@ -10584,23 +10584,23 @@
       <c r="LT155" t="s">
         <v>673</v>
       </c>
+      <c r="LU155" t="s">
+        <v>660</v>
+      </c>
       <c r="LW155" t="s">
-        <v>22</v>
+        <v>661</v>
       </c>
       <c r="LX155" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY155" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ155" t="s">
-        <v>660</v>
+        <v>25</v>
       </c>
       <c r="MA155" t="s">
-        <v>661</v>
+        <v>674</v>
       </c>
       <c r="MB155" t="s">
-        <v>674</v>
+        <v>526</v>
       </c>
       <c r="MC155" t="s">
         <v>28</v>
@@ -10619,23 +10619,23 @@
       <c r="LT156" t="s">
         <v>677</v>
       </c>
+      <c r="LU156" t="s">
+        <v>660</v>
+      </c>
       <c r="LW156" t="s">
-        <v>22</v>
+        <v>661</v>
       </c>
       <c r="LX156" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY156" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ156" t="s">
-        <v>660</v>
+        <v>25</v>
       </c>
       <c r="MA156" t="s">
-        <v>661</v>
+        <v>678</v>
       </c>
       <c r="MB156" t="s">
-        <v>678</v>
+        <v>526</v>
       </c>
       <c r="MC156" t="s">
         <v>28</v>
@@ -10654,23 +10654,23 @@
       <c r="LT157" t="s">
         <v>681</v>
       </c>
+      <c r="LU157" t="s">
+        <v>660</v>
+      </c>
       <c r="LW157" t="s">
-        <v>22</v>
+        <v>661</v>
       </c>
       <c r="LX157" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY157" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ157" t="s">
-        <v>660</v>
+        <v>25</v>
       </c>
       <c r="MA157" t="s">
-        <v>661</v>
+        <v>682</v>
       </c>
       <c r="MB157" t="s">
-        <v>682</v>
+        <v>526</v>
       </c>
       <c r="MC157" t="s">
         <v>28</v>
@@ -10689,23 +10689,23 @@
       <c r="LT158" t="s">
         <v>685</v>
       </c>
+      <c r="LU158" t="s">
+        <v>660</v>
+      </c>
       <c r="LW158" t="s">
-        <v>22</v>
+        <v>661</v>
       </c>
       <c r="LX158" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY158" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ158" t="s">
-        <v>660</v>
+        <v>25</v>
       </c>
       <c r="MA158" t="s">
-        <v>661</v>
+        <v>686</v>
       </c>
       <c r="MB158" t="s">
-        <v>686</v>
+        <v>526</v>
       </c>
       <c r="MC158" t="s">
         <v>28</v>
@@ -10724,23 +10724,23 @@
       <c r="LT159" t="s">
         <v>689</v>
       </c>
+      <c r="LU159" t="s">
+        <v>660</v>
+      </c>
       <c r="LW159" t="s">
-        <v>22</v>
+        <v>661</v>
       </c>
       <c r="LX159" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY159" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ159" t="s">
-        <v>660</v>
+        <v>25</v>
       </c>
       <c r="MA159" t="s">
-        <v>661</v>
+        <v>690</v>
       </c>
       <c r="MB159" t="s">
-        <v>690</v>
+        <v>526</v>
       </c>
       <c r="MC159" t="s">
         <v>28</v>
@@ -10759,23 +10759,23 @@
       <c r="LT160" t="s">
         <v>693</v>
       </c>
+      <c r="LU160" t="s">
+        <v>660</v>
+      </c>
       <c r="LW160" t="s">
-        <v>22</v>
+        <v>661</v>
       </c>
       <c r="LX160" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY160" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ160" t="s">
-        <v>660</v>
+        <v>25</v>
       </c>
       <c r="MA160" t="s">
-        <v>661</v>
+        <v>694</v>
       </c>
       <c r="MB160" t="s">
-        <v>694</v>
+        <v>526</v>
       </c>
       <c r="MC160" t="s">
         <v>28</v>
@@ -10794,23 +10794,23 @@
       <c r="LT161" t="s">
         <v>697</v>
       </c>
+      <c r="LU161" t="s">
+        <v>660</v>
+      </c>
       <c r="LW161" t="s">
-        <v>22</v>
+        <v>661</v>
       </c>
       <c r="LX161" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY161" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ161" t="s">
-        <v>660</v>
+        <v>25</v>
       </c>
       <c r="MA161" t="s">
-        <v>661</v>
+        <v>698</v>
       </c>
       <c r="MB161" t="s">
-        <v>698</v>
+        <v>526</v>
       </c>
       <c r="MC161" t="s">
         <v>28</v>
@@ -10829,23 +10829,23 @@
       <c r="LT162" t="s">
         <v>701</v>
       </c>
+      <c r="LU162" t="s">
+        <v>660</v>
+      </c>
       <c r="LW162" t="s">
-        <v>22</v>
+        <v>661</v>
       </c>
       <c r="LX162" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY162" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ162" t="s">
-        <v>660</v>
+        <v>25</v>
       </c>
       <c r="MA162" t="s">
-        <v>661</v>
+        <v>702</v>
       </c>
       <c r="MB162" t="s">
-        <v>702</v>
+        <v>526</v>
       </c>
       <c r="MC162" t="s">
         <v>28</v>
@@ -10864,23 +10864,23 @@
       <c r="LT163" t="s">
         <v>705</v>
       </c>
+      <c r="LU163" t="s">
+        <v>660</v>
+      </c>
       <c r="LW163" t="s">
-        <v>22</v>
+        <v>661</v>
       </c>
       <c r="LX163" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY163" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ163" t="s">
-        <v>660</v>
+        <v>25</v>
       </c>
       <c r="MA163" t="s">
-        <v>661</v>
+        <v>706</v>
       </c>
       <c r="MB163" t="s">
-        <v>706</v>
+        <v>526</v>
       </c>
       <c r="MC163" t="s">
         <v>28</v>
@@ -10899,23 +10899,23 @@
       <c r="LT164" t="s">
         <v>709</v>
       </c>
+      <c r="LU164" t="s">
+        <v>660</v>
+      </c>
       <c r="LW164" t="s">
-        <v>22</v>
+        <v>661</v>
       </c>
       <c r="LX164" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY164" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ164" t="s">
-        <v>660</v>
+        <v>25</v>
       </c>
       <c r="MA164" t="s">
-        <v>661</v>
+        <v>710</v>
       </c>
       <c r="MB164" t="s">
-        <v>710</v>
+        <v>526</v>
       </c>
       <c r="MC164" t="s">
         <v>28</v>
@@ -10934,23 +10934,23 @@
       <c r="LT165" t="s">
         <v>713</v>
       </c>
+      <c r="LU165" t="s">
+        <v>660</v>
+      </c>
       <c r="LW165" t="s">
-        <v>22</v>
+        <v>661</v>
       </c>
       <c r="LX165" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY165" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ165" t="s">
-        <v>660</v>
+        <v>25</v>
       </c>
       <c r="MA165" t="s">
-        <v>661</v>
+        <v>714</v>
       </c>
       <c r="MB165" t="s">
-        <v>714</v>
+        <v>526</v>
       </c>
       <c r="MC165" t="s">
         <v>28</v>
@@ -10969,23 +10969,23 @@
       <c r="LT166" t="s">
         <v>717</v>
       </c>
+      <c r="LU166" t="s">
+        <v>660</v>
+      </c>
       <c r="LW166" t="s">
-        <v>22</v>
+        <v>661</v>
       </c>
       <c r="LX166" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY166" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ166" t="s">
-        <v>660</v>
+        <v>25</v>
       </c>
       <c r="MA166" t="s">
-        <v>661</v>
+        <v>718</v>
       </c>
       <c r="MB166" t="s">
-        <v>718</v>
+        <v>526</v>
       </c>
       <c r="MC166" t="s">
         <v>28</v>
@@ -11004,23 +11004,23 @@
       <c r="LT167" t="s">
         <v>721</v>
       </c>
+      <c r="LU167" t="s">
+        <v>660</v>
+      </c>
       <c r="LW167" t="s">
-        <v>22</v>
+        <v>661</v>
       </c>
       <c r="LX167" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY167" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ167" t="s">
-        <v>660</v>
+        <v>25</v>
       </c>
       <c r="MA167" t="s">
-        <v>661</v>
+        <v>722</v>
       </c>
       <c r="MB167" t="s">
-        <v>722</v>
+        <v>526</v>
       </c>
       <c r="MC167" t="s">
         <v>28</v>
@@ -11039,23 +11039,23 @@
       <c r="LT168" t="s">
         <v>725</v>
       </c>
+      <c r="LU168" t="s">
+        <v>660</v>
+      </c>
       <c r="LW168" t="s">
-        <v>22</v>
+        <v>661</v>
       </c>
       <c r="LX168" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY168" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ168" t="s">
-        <v>660</v>
+        <v>25</v>
       </c>
       <c r="MA168" t="s">
-        <v>661</v>
+        <v>726</v>
       </c>
       <c r="MB168" t="s">
-        <v>726</v>
+        <v>526</v>
       </c>
       <c r="MC168" t="s">
         <v>28</v>
@@ -11074,23 +11074,23 @@
       <c r="LT169" t="s">
         <v>729</v>
       </c>
+      <c r="LU169" t="s">
+        <v>660</v>
+      </c>
       <c r="LW169" t="s">
-        <v>22</v>
+        <v>661</v>
       </c>
       <c r="LX169" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="LY169" t="s">
-        <v>523</v>
-      </c>
-      <c r="LZ169" t="s">
-        <v>660</v>
+        <v>25</v>
       </c>
       <c r="MA169" t="s">
-        <v>661</v>
+        <v>730</v>
       </c>
       <c r="MB169" t="s">
-        <v>730</v>
+        <v>526</v>
       </c>
       <c r="MC169" t="s">
         <v>28</v>
@@ -11109,17 +11109,17 @@
       <c r="LT170" t="s">
         <v>733</v>
       </c>
+      <c r="LU170" t="s">
+        <v>734</v>
+      </c>
       <c r="LW170" t="s">
-        <v>22</v>
+        <v>735</v>
       </c>
       <c r="LX170" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY170" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ170" t="s">
-        <v>736</v>
+        <v>25</v>
       </c>
       <c r="MA170" t="s">
         <v>737</v>
@@ -11144,23 +11144,23 @@
       <c r="LT171" t="s">
         <v>741</v>
       </c>
+      <c r="LU171" t="s">
+        <v>734</v>
+      </c>
       <c r="LW171" t="s">
-        <v>22</v>
+        <v>735</v>
       </c>
       <c r="LX171" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY171" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ171" t="s">
-        <v>736</v>
+        <v>25</v>
       </c>
       <c r="MA171" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="MB171" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="MC171" t="s">
         <v>28</v>
@@ -11179,23 +11179,23 @@
       <c r="LT172" t="s">
         <v>745</v>
       </c>
+      <c r="LU172" t="s">
+        <v>734</v>
+      </c>
       <c r="LW172" t="s">
-        <v>22</v>
+        <v>735</v>
       </c>
       <c r="LX172" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY172" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ172" t="s">
-        <v>736</v>
+        <v>25</v>
       </c>
       <c r="MA172" t="s">
-        <v>737</v>
+        <v>746</v>
       </c>
       <c r="MB172" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
       <c r="MC172" t="s">
         <v>28</v>
@@ -11214,23 +11214,23 @@
       <c r="LT173" t="s">
         <v>749</v>
       </c>
+      <c r="LU173" t="s">
+        <v>734</v>
+      </c>
       <c r="LW173" t="s">
-        <v>22</v>
+        <v>735</v>
       </c>
       <c r="LX173" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY173" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ173" t="s">
-        <v>736</v>
+        <v>25</v>
       </c>
       <c r="MA173" t="s">
-        <v>737</v>
+        <v>750</v>
       </c>
       <c r="MB173" t="s">
-        <v>750</v>
+        <v>738</v>
       </c>
       <c r="MC173" t="s">
         <v>28</v>
@@ -11249,23 +11249,23 @@
       <c r="LT174" t="s">
         <v>753</v>
       </c>
+      <c r="LU174" t="s">
+        <v>734</v>
+      </c>
       <c r="LW174" t="s">
-        <v>22</v>
+        <v>735</v>
       </c>
       <c r="LX174" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY174" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ174" t="s">
-        <v>736</v>
+        <v>25</v>
       </c>
       <c r="MA174" t="s">
-        <v>737</v>
+        <v>754</v>
       </c>
       <c r="MB174" t="s">
-        <v>754</v>
+        <v>738</v>
       </c>
       <c r="MC174" t="s">
         <v>28</v>
@@ -11284,23 +11284,23 @@
       <c r="LT175" t="s">
         <v>757</v>
       </c>
+      <c r="LU175" t="s">
+        <v>734</v>
+      </c>
       <c r="LW175" t="s">
-        <v>22</v>
+        <v>735</v>
       </c>
       <c r="LX175" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY175" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ175" t="s">
-        <v>736</v>
+        <v>25</v>
       </c>
       <c r="MA175" t="s">
-        <v>737</v>
+        <v>758</v>
       </c>
       <c r="MB175" t="s">
-        <v>758</v>
+        <v>738</v>
       </c>
       <c r="MC175" t="s">
         <v>28</v>
@@ -11319,23 +11319,23 @@
       <c r="LT176" t="s">
         <v>761</v>
       </c>
+      <c r="LU176" t="s">
+        <v>734</v>
+      </c>
       <c r="LW176" t="s">
-        <v>22</v>
+        <v>735</v>
       </c>
       <c r="LX176" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY176" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ176" t="s">
-        <v>736</v>
+        <v>25</v>
       </c>
       <c r="MA176" t="s">
-        <v>737</v>
+        <v>762</v>
       </c>
       <c r="MB176" t="s">
-        <v>762</v>
+        <v>738</v>
       </c>
       <c r="MC176" t="s">
         <v>28</v>
@@ -11354,23 +11354,23 @@
       <c r="LT177" t="s">
         <v>765</v>
       </c>
+      <c r="LU177" t="s">
+        <v>734</v>
+      </c>
       <c r="LW177" t="s">
-        <v>22</v>
+        <v>735</v>
       </c>
       <c r="LX177" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY177" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ177" t="s">
-        <v>736</v>
+        <v>25</v>
       </c>
       <c r="MA177" t="s">
-        <v>737</v>
+        <v>766</v>
       </c>
       <c r="MB177" t="s">
-        <v>766</v>
+        <v>738</v>
       </c>
       <c r="MC177" t="s">
         <v>28</v>
@@ -11389,23 +11389,23 @@
       <c r="LT178" t="s">
         <v>769</v>
       </c>
+      <c r="LU178" t="s">
+        <v>734</v>
+      </c>
       <c r="LW178" t="s">
-        <v>22</v>
+        <v>735</v>
       </c>
       <c r="LX178" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY178" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ178" t="s">
-        <v>736</v>
+        <v>25</v>
       </c>
       <c r="MA178" t="s">
-        <v>737</v>
+        <v>770</v>
       </c>
       <c r="MB178" t="s">
-        <v>770</v>
+        <v>738</v>
       </c>
       <c r="MC178" t="s">
         <v>28</v>
@@ -11424,23 +11424,23 @@
       <c r="LT179" t="s">
         <v>773</v>
       </c>
+      <c r="LU179" t="s">
+        <v>734</v>
+      </c>
       <c r="LW179" t="s">
-        <v>22</v>
+        <v>735</v>
       </c>
       <c r="LX179" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY179" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ179" t="s">
-        <v>736</v>
+        <v>25</v>
       </c>
       <c r="MA179" t="s">
-        <v>737</v>
+        <v>774</v>
       </c>
       <c r="MB179" t="s">
-        <v>774</v>
+        <v>738</v>
       </c>
       <c r="MC179" t="s">
         <v>28</v>
@@ -11459,23 +11459,23 @@
       <c r="LT180" t="s">
         <v>777</v>
       </c>
+      <c r="LU180" t="s">
+        <v>778</v>
+      </c>
       <c r="LW180" t="s">
-        <v>22</v>
+        <v>779</v>
       </c>
       <c r="LX180" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY180" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ180" t="s">
-        <v>778</v>
+        <v>25</v>
       </c>
       <c r="MA180" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="MB180" t="s">
-        <v>780</v>
+        <v>738</v>
       </c>
       <c r="MC180" t="s">
         <v>28</v>
@@ -11495,28 +11495,28 @@
         <v>783</v>
       </c>
       <c r="LU181" t="s">
+        <v>778</v>
+      </c>
+      <c r="LV181" t="s">
         <v>784</v>
       </c>
-      <c r="LV181" t="s">
+      <c r="LW181" t="s">
+        <v>779</v>
+      </c>
+      <c r="LX181" t="s">
+        <v>736</v>
+      </c>
+      <c r="LY181" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ181" t="s">
         <v>785</v>
       </c>
-      <c r="LW181" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX181" t="s">
-        <v>734</v>
-      </c>
-      <c r="LY181" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ181" t="s">
-        <v>778</v>
-      </c>
       <c r="MA181" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="MB181" t="s">
-        <v>786</v>
+        <v>738</v>
       </c>
       <c r="MC181" t="s">
         <v>28</v>
@@ -11536,28 +11536,28 @@
         <v>789</v>
       </c>
       <c r="LU182" t="s">
+        <v>778</v>
+      </c>
+      <c r="LV182" t="s">
         <v>784</v>
       </c>
-      <c r="LV182" t="s">
+      <c r="LW182" t="s">
+        <v>779</v>
+      </c>
+      <c r="LX182" t="s">
+        <v>736</v>
+      </c>
+      <c r="LY182" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ182" t="s">
         <v>785</v>
       </c>
-      <c r="LW182" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX182" t="s">
-        <v>734</v>
-      </c>
-      <c r="LY182" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ182" t="s">
-        <v>778</v>
-      </c>
       <c r="MA182" t="s">
-        <v>779</v>
+        <v>790</v>
       </c>
       <c r="MB182" t="s">
-        <v>790</v>
+        <v>738</v>
       </c>
       <c r="MC182" t="s">
         <v>28</v>
@@ -11574,25 +11574,25 @@
         <v>20</v>
       </c>
       <c r="LU183" t="s">
+        <v>778</v>
+      </c>
+      <c r="LV183" t="s">
         <v>784</v>
       </c>
-      <c r="LV183" t="s">
+      <c r="LW183" t="s">
+        <v>779</v>
+      </c>
+      <c r="LX183" t="s">
+        <v>736</v>
+      </c>
+      <c r="LY183" t="s">
+        <v>25</v>
+      </c>
+      <c r="LZ183" t="s">
         <v>785</v>
       </c>
-      <c r="LW183" t="s">
-        <v>22</v>
-      </c>
-      <c r="LX183" t="s">
-        <v>734</v>
-      </c>
-      <c r="LY183" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ183" t="s">
-        <v>778</v>
-      </c>
-      <c r="MA183" t="s">
-        <v>779</v>
+      <c r="MB183" t="s">
+        <v>738</v>
       </c>
       <c r="MC183" t="s">
         <v>28</v>
@@ -11611,23 +11611,23 @@
       <c r="LT184" t="s">
         <v>795</v>
       </c>
+      <c r="LU184" t="s">
+        <v>778</v>
+      </c>
       <c r="LW184" t="s">
-        <v>22</v>
+        <v>779</v>
       </c>
       <c r="LX184" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY184" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ184" t="s">
-        <v>778</v>
+        <v>25</v>
       </c>
       <c r="MA184" t="s">
-        <v>779</v>
+        <v>796</v>
       </c>
       <c r="MB184" t="s">
-        <v>796</v>
+        <v>738</v>
       </c>
       <c r="MC184" t="s">
         <v>28</v>
@@ -11646,23 +11646,23 @@
       <c r="LT185" t="s">
         <v>799</v>
       </c>
+      <c r="LU185" t="s">
+        <v>778</v>
+      </c>
       <c r="LW185" t="s">
-        <v>22</v>
+        <v>779</v>
       </c>
       <c r="LX185" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY185" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ185" t="s">
-        <v>778</v>
+        <v>25</v>
       </c>
       <c r="MA185" t="s">
-        <v>779</v>
+        <v>800</v>
       </c>
       <c r="MB185" t="s">
-        <v>800</v>
+        <v>738</v>
       </c>
       <c r="MC185" t="s">
         <v>28</v>
@@ -11681,23 +11681,23 @@
       <c r="LT186" t="s">
         <v>803</v>
       </c>
+      <c r="LU186" t="s">
+        <v>778</v>
+      </c>
       <c r="LW186" t="s">
-        <v>22</v>
+        <v>779</v>
       </c>
       <c r="LX186" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY186" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ186" t="s">
-        <v>778</v>
+        <v>25</v>
       </c>
       <c r="MA186" t="s">
-        <v>779</v>
+        <v>804</v>
       </c>
       <c r="MB186" t="s">
-        <v>804</v>
+        <v>738</v>
       </c>
       <c r="MC186" t="s">
         <v>28</v>
@@ -11716,23 +11716,23 @@
       <c r="LT187" t="s">
         <v>807</v>
       </c>
+      <c r="LU187" t="s">
+        <v>778</v>
+      </c>
       <c r="LW187" t="s">
-        <v>22</v>
+        <v>779</v>
       </c>
       <c r="LX187" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY187" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ187" t="s">
-        <v>778</v>
+        <v>25</v>
       </c>
       <c r="MA187" t="s">
-        <v>779</v>
+        <v>808</v>
       </c>
       <c r="MB187" t="s">
-        <v>808</v>
+        <v>738</v>
       </c>
       <c r="MC187" t="s">
         <v>28</v>
@@ -11751,23 +11751,23 @@
       <c r="LT188" t="s">
         <v>811</v>
       </c>
+      <c r="LU188" t="s">
+        <v>778</v>
+      </c>
       <c r="LW188" t="s">
-        <v>22</v>
+        <v>779</v>
       </c>
       <c r="LX188" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY188" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ188" t="s">
-        <v>778</v>
+        <v>25</v>
       </c>
       <c r="MA188" t="s">
-        <v>779</v>
+        <v>812</v>
       </c>
       <c r="MB188" t="s">
-        <v>812</v>
+        <v>738</v>
       </c>
       <c r="MC188" t="s">
         <v>28</v>
@@ -11786,23 +11786,23 @@
       <c r="LT189" t="s">
         <v>815</v>
       </c>
+      <c r="LU189" t="s">
+        <v>778</v>
+      </c>
       <c r="LW189" t="s">
-        <v>22</v>
+        <v>779</v>
       </c>
       <c r="LX189" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY189" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ189" t="s">
-        <v>778</v>
+        <v>25</v>
       </c>
       <c r="MA189" t="s">
-        <v>779</v>
+        <v>816</v>
       </c>
       <c r="MB189" t="s">
-        <v>816</v>
+        <v>738</v>
       </c>
       <c r="MC189" t="s">
         <v>28</v>
@@ -11821,23 +11821,23 @@
       <c r="LT190" t="s">
         <v>819</v>
       </c>
+      <c r="LU190" t="s">
+        <v>778</v>
+      </c>
       <c r="LW190" t="s">
-        <v>22</v>
+        <v>779</v>
       </c>
       <c r="LX190" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY190" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ190" t="s">
-        <v>778</v>
+        <v>25</v>
       </c>
       <c r="MA190" t="s">
-        <v>779</v>
+        <v>820</v>
       </c>
       <c r="MB190" t="s">
-        <v>820</v>
+        <v>738</v>
       </c>
       <c r="MC190" t="s">
         <v>28</v>
@@ -11856,23 +11856,23 @@
       <c r="LT191" t="s">
         <v>823</v>
       </c>
+      <c r="LU191" t="s">
+        <v>778</v>
+      </c>
       <c r="LW191" t="s">
-        <v>22</v>
+        <v>779</v>
       </c>
       <c r="LX191" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY191" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ191" t="s">
-        <v>778</v>
+        <v>25</v>
       </c>
       <c r="MA191" t="s">
-        <v>779</v>
+        <v>824</v>
       </c>
       <c r="MB191" t="s">
-        <v>824</v>
+        <v>738</v>
       </c>
       <c r="MC191" t="s">
         <v>28</v>
@@ -11891,23 +11891,23 @@
       <c r="LT192" t="s">
         <v>827</v>
       </c>
+      <c r="LU192" t="s">
+        <v>778</v>
+      </c>
       <c r="LW192" t="s">
-        <v>22</v>
+        <v>779</v>
       </c>
       <c r="LX192" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY192" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ192" t="s">
-        <v>778</v>
+        <v>25</v>
       </c>
       <c r="MA192" t="s">
-        <v>779</v>
+        <v>828</v>
       </c>
       <c r="MB192" t="s">
-        <v>828</v>
+        <v>738</v>
       </c>
       <c r="MC192" t="s">
         <v>28</v>
@@ -11926,23 +11926,23 @@
       <c r="LT193" t="s">
         <v>831</v>
       </c>
+      <c r="LU193" t="s">
+        <v>778</v>
+      </c>
       <c r="LW193" t="s">
-        <v>22</v>
+        <v>779</v>
       </c>
       <c r="LX193" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY193" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ193" t="s">
-        <v>778</v>
+        <v>25</v>
       </c>
       <c r="MA193" t="s">
-        <v>779</v>
+        <v>832</v>
       </c>
       <c r="MB193" t="s">
-        <v>832</v>
+        <v>738</v>
       </c>
       <c r="MC193" t="s">
         <v>28</v>
@@ -11961,23 +11961,23 @@
       <c r="LT194" t="s">
         <v>835</v>
       </c>
+      <c r="LU194" t="s">
+        <v>778</v>
+      </c>
       <c r="LW194" t="s">
-        <v>22</v>
+        <v>779</v>
       </c>
       <c r="LX194" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY194" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ194" t="s">
-        <v>778</v>
+        <v>25</v>
       </c>
       <c r="MA194" t="s">
-        <v>779</v>
+        <v>836</v>
       </c>
       <c r="MB194" t="s">
-        <v>836</v>
+        <v>738</v>
       </c>
       <c r="MC194" t="s">
         <v>28</v>
@@ -11996,23 +11996,23 @@
       <c r="LT195" t="s">
         <v>839</v>
       </c>
+      <c r="LU195" t="s">
+        <v>778</v>
+      </c>
       <c r="LW195" t="s">
-        <v>22</v>
+        <v>779</v>
       </c>
       <c r="LX195" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY195" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ195" t="s">
-        <v>778</v>
+        <v>25</v>
       </c>
       <c r="MA195" t="s">
-        <v>779</v>
+        <v>840</v>
       </c>
       <c r="MB195" t="s">
-        <v>840</v>
+        <v>738</v>
       </c>
       <c r="MC195" t="s">
         <v>28</v>
@@ -12031,23 +12031,23 @@
       <c r="LT196" t="s">
         <v>843</v>
       </c>
+      <c r="LU196" t="s">
+        <v>778</v>
+      </c>
       <c r="LW196" t="s">
-        <v>22</v>
+        <v>779</v>
       </c>
       <c r="LX196" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY196" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ196" t="s">
-        <v>778</v>
+        <v>25</v>
       </c>
       <c r="MA196" t="s">
-        <v>779</v>
+        <v>844</v>
       </c>
       <c r="MB196" t="s">
-        <v>844</v>
+        <v>738</v>
       </c>
       <c r="MC196" t="s">
         <v>28</v>
@@ -12066,23 +12066,23 @@
       <c r="LT197" t="s">
         <v>847</v>
       </c>
+      <c r="LU197" t="s">
+        <v>848</v>
+      </c>
       <c r="LW197" t="s">
-        <v>22</v>
+        <v>849</v>
       </c>
       <c r="LX197" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY197" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ197" t="s">
-        <v>848</v>
+        <v>25</v>
       </c>
       <c r="MA197" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="MB197" t="s">
-        <v>850</v>
+        <v>738</v>
       </c>
       <c r="MC197" t="s">
         <v>28</v>
@@ -12101,23 +12101,23 @@
       <c r="LT198" t="s">
         <v>853</v>
       </c>
+      <c r="LU198" t="s">
+        <v>848</v>
+      </c>
       <c r="LW198" t="s">
-        <v>22</v>
+        <v>849</v>
       </c>
       <c r="LX198" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY198" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ198" t="s">
-        <v>848</v>
+        <v>25</v>
       </c>
       <c r="MA198" t="s">
-        <v>849</v>
+        <v>854</v>
       </c>
       <c r="MB198" t="s">
-        <v>854</v>
+        <v>738</v>
       </c>
       <c r="MC198" t="s">
         <v>28</v>
@@ -12136,23 +12136,23 @@
       <c r="LT199" t="s">
         <v>857</v>
       </c>
+      <c r="LU199" t="s">
+        <v>848</v>
+      </c>
       <c r="LW199" t="s">
-        <v>22</v>
+        <v>849</v>
       </c>
       <c r="LX199" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY199" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ199" t="s">
-        <v>848</v>
+        <v>25</v>
       </c>
       <c r="MA199" t="s">
-        <v>849</v>
+        <v>858</v>
       </c>
       <c r="MB199" t="s">
-        <v>858</v>
+        <v>738</v>
       </c>
       <c r="MC199" t="s">
         <v>28</v>
@@ -12171,23 +12171,23 @@
       <c r="LT200" t="s">
         <v>861</v>
       </c>
+      <c r="LU200" t="s">
+        <v>848</v>
+      </c>
       <c r="LW200" t="s">
-        <v>22</v>
+        <v>849</v>
       </c>
       <c r="LX200" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY200" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ200" t="s">
-        <v>848</v>
+        <v>25</v>
       </c>
       <c r="MA200" t="s">
-        <v>849</v>
+        <v>862</v>
       </c>
       <c r="MB200" t="s">
-        <v>862</v>
+        <v>738</v>
       </c>
       <c r="MC200" t="s">
         <v>28</v>
@@ -12206,23 +12206,23 @@
       <c r="LT201" t="s">
         <v>865</v>
       </c>
+      <c r="LU201" t="s">
+        <v>848</v>
+      </c>
       <c r="LW201" t="s">
-        <v>22</v>
+        <v>849</v>
       </c>
       <c r="LX201" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY201" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ201" t="s">
-        <v>848</v>
+        <v>25</v>
       </c>
       <c r="MA201" t="s">
-        <v>849</v>
+        <v>866</v>
       </c>
       <c r="MB201" t="s">
-        <v>866</v>
+        <v>738</v>
       </c>
       <c r="MC201" t="s">
         <v>28</v>
@@ -12241,23 +12241,23 @@
       <c r="LT202" t="s">
         <v>869</v>
       </c>
+      <c r="LU202" t="s">
+        <v>848</v>
+      </c>
       <c r="LW202" t="s">
-        <v>22</v>
+        <v>849</v>
       </c>
       <c r="LX202" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY202" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ202" t="s">
-        <v>848</v>
+        <v>25</v>
       </c>
       <c r="MA202" t="s">
-        <v>849</v>
+        <v>870</v>
       </c>
       <c r="MB202" t="s">
-        <v>870</v>
+        <v>738</v>
       </c>
       <c r="MC202" t="s">
         <v>28</v>
@@ -12276,23 +12276,23 @@
       <c r="LT203" t="s">
         <v>873</v>
       </c>
+      <c r="LU203" t="s">
+        <v>848</v>
+      </c>
       <c r="LW203" t="s">
-        <v>22</v>
+        <v>849</v>
       </c>
       <c r="LX203" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY203" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ203" t="s">
-        <v>848</v>
+        <v>25</v>
       </c>
       <c r="MA203" t="s">
-        <v>849</v>
+        <v>874</v>
       </c>
       <c r="MB203" t="s">
-        <v>874</v>
+        <v>738</v>
       </c>
       <c r="MC203" t="s">
         <v>28</v>
@@ -12311,23 +12311,23 @@
       <c r="LT204" t="s">
         <v>877</v>
       </c>
+      <c r="LU204" t="s">
+        <v>848</v>
+      </c>
       <c r="LW204" t="s">
-        <v>22</v>
+        <v>849</v>
       </c>
       <c r="LX204" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY204" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ204" t="s">
-        <v>848</v>
+        <v>25</v>
       </c>
       <c r="MA204" t="s">
-        <v>849</v>
+        <v>878</v>
       </c>
       <c r="MB204" t="s">
-        <v>878</v>
+        <v>738</v>
       </c>
       <c r="MC204" t="s">
         <v>28</v>
@@ -12346,23 +12346,23 @@
       <c r="LT205" t="s">
         <v>881</v>
       </c>
+      <c r="LU205" t="s">
+        <v>848</v>
+      </c>
       <c r="LW205" t="s">
-        <v>22</v>
+        <v>849</v>
       </c>
       <c r="LX205" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY205" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ205" t="s">
-        <v>848</v>
+        <v>25</v>
       </c>
       <c r="MA205" t="s">
-        <v>849</v>
+        <v>882</v>
       </c>
       <c r="MB205" t="s">
-        <v>882</v>
+        <v>738</v>
       </c>
       <c r="MC205" t="s">
         <v>28</v>
@@ -12381,23 +12381,23 @@
       <c r="LT206" t="s">
         <v>885</v>
       </c>
+      <c r="LU206" t="s">
+        <v>848</v>
+      </c>
       <c r="LW206" t="s">
-        <v>22</v>
+        <v>849</v>
       </c>
       <c r="LX206" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY206" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ206" t="s">
-        <v>848</v>
+        <v>25</v>
       </c>
       <c r="MA206" t="s">
-        <v>849</v>
+        <v>886</v>
       </c>
       <c r="MB206" t="s">
-        <v>886</v>
+        <v>738</v>
       </c>
       <c r="MC206" t="s">
         <v>28</v>
@@ -12416,23 +12416,23 @@
       <c r="LT207" t="s">
         <v>889</v>
       </c>
+      <c r="LU207" t="s">
+        <v>848</v>
+      </c>
       <c r="LW207" t="s">
-        <v>22</v>
+        <v>849</v>
       </c>
       <c r="LX207" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY207" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ207" t="s">
-        <v>848</v>
+        <v>25</v>
       </c>
       <c r="MA207" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
       <c r="MB207" t="s">
-        <v>890</v>
+        <v>738</v>
       </c>
       <c r="MC207" t="s">
         <v>28</v>
@@ -12451,23 +12451,23 @@
       <c r="LT208" t="s">
         <v>893</v>
       </c>
+      <c r="LU208" t="s">
+        <v>848</v>
+      </c>
       <c r="LW208" t="s">
-        <v>22</v>
+        <v>849</v>
       </c>
       <c r="LX208" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY208" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ208" t="s">
-        <v>848</v>
+        <v>25</v>
       </c>
       <c r="MA208" t="s">
-        <v>849</v>
+        <v>894</v>
       </c>
       <c r="MB208" t="s">
-        <v>894</v>
+        <v>738</v>
       </c>
       <c r="MC208" t="s">
         <v>28</v>
@@ -12486,23 +12486,23 @@
       <c r="LT209" t="s">
         <v>897</v>
       </c>
+      <c r="LU209" t="s">
+        <v>848</v>
+      </c>
       <c r="LW209" t="s">
-        <v>22</v>
+        <v>849</v>
       </c>
       <c r="LX209" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY209" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ209" t="s">
-        <v>848</v>
+        <v>25</v>
       </c>
       <c r="MA209" t="s">
-        <v>849</v>
+        <v>898</v>
       </c>
       <c r="MB209" t="s">
-        <v>898</v>
+        <v>738</v>
       </c>
       <c r="MC209" t="s">
         <v>28</v>
@@ -12521,23 +12521,23 @@
       <c r="LT210" t="s">
         <v>901</v>
       </c>
+      <c r="LU210" t="s">
+        <v>848</v>
+      </c>
       <c r="LW210" t="s">
-        <v>22</v>
+        <v>849</v>
       </c>
       <c r="LX210" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY210" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ210" t="s">
-        <v>848</v>
+        <v>25</v>
       </c>
       <c r="MA210" t="s">
-        <v>849</v>
+        <v>902</v>
       </c>
       <c r="MB210" t="s">
-        <v>902</v>
+        <v>738</v>
       </c>
       <c r="MC210" t="s">
         <v>28</v>
@@ -12556,23 +12556,23 @@
       <c r="LT211" t="s">
         <v>905</v>
       </c>
+      <c r="LU211" t="s">
+        <v>848</v>
+      </c>
       <c r="LW211" t="s">
-        <v>22</v>
+        <v>849</v>
       </c>
       <c r="LX211" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY211" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ211" t="s">
-        <v>848</v>
+        <v>25</v>
       </c>
       <c r="MA211" t="s">
-        <v>849</v>
+        <v>906</v>
       </c>
       <c r="MB211" t="s">
-        <v>906</v>
+        <v>738</v>
       </c>
       <c r="MC211" t="s">
         <v>28</v>
@@ -12591,23 +12591,23 @@
       <c r="LT212" t="s">
         <v>909</v>
       </c>
+      <c r="LU212" t="s">
+        <v>848</v>
+      </c>
       <c r="LW212" t="s">
-        <v>22</v>
+        <v>849</v>
       </c>
       <c r="LX212" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY212" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ212" t="s">
-        <v>848</v>
+        <v>25</v>
       </c>
       <c r="MA212" t="s">
-        <v>849</v>
+        <v>910</v>
       </c>
       <c r="MB212" t="s">
-        <v>910</v>
+        <v>738</v>
       </c>
       <c r="MC212" t="s">
         <v>28</v>
@@ -12626,23 +12626,23 @@
       <c r="LT213" t="s">
         <v>913</v>
       </c>
+      <c r="LU213" t="s">
+        <v>914</v>
+      </c>
       <c r="LW213" t="s">
-        <v>22</v>
+        <v>915</v>
       </c>
       <c r="LX213" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY213" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ213" t="s">
-        <v>914</v>
+        <v>25</v>
       </c>
       <c r="MA213" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="MB213" t="s">
-        <v>916</v>
+        <v>738</v>
       </c>
       <c r="MC213" t="s">
         <v>28</v>
@@ -12661,23 +12661,23 @@
       <c r="LT214" t="s">
         <v>919</v>
       </c>
+      <c r="LU214" t="s">
+        <v>914</v>
+      </c>
       <c r="LW214" t="s">
-        <v>22</v>
+        <v>915</v>
       </c>
       <c r="LX214" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY214" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ214" t="s">
-        <v>914</v>
+        <v>25</v>
       </c>
       <c r="MA214" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="MB214" t="s">
-        <v>920</v>
+        <v>738</v>
       </c>
       <c r="MC214" t="s">
         <v>28</v>
@@ -12696,23 +12696,23 @@
       <c r="LT215" t="s">
         <v>923</v>
       </c>
+      <c r="LU215" t="s">
+        <v>914</v>
+      </c>
       <c r="LW215" t="s">
-        <v>22</v>
+        <v>915</v>
       </c>
       <c r="LX215" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY215" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ215" t="s">
-        <v>914</v>
+        <v>25</v>
       </c>
       <c r="MA215" t="s">
-        <v>915</v>
+        <v>924</v>
       </c>
       <c r="MB215" t="s">
-        <v>924</v>
+        <v>738</v>
       </c>
       <c r="MC215" t="s">
         <v>28</v>
@@ -12731,23 +12731,23 @@
       <c r="LT216" t="s">
         <v>927</v>
       </c>
+      <c r="LU216" t="s">
+        <v>914</v>
+      </c>
       <c r="LW216" t="s">
-        <v>22</v>
+        <v>915</v>
       </c>
       <c r="LX216" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY216" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ216" t="s">
-        <v>914</v>
+        <v>25</v>
       </c>
       <c r="MA216" t="s">
-        <v>915</v>
+        <v>928</v>
       </c>
       <c r="MB216" t="s">
-        <v>928</v>
+        <v>738</v>
       </c>
       <c r="MC216" t="s">
         <v>28</v>
@@ -12766,23 +12766,23 @@
       <c r="LT217" t="s">
         <v>931</v>
       </c>
+      <c r="LU217" t="s">
+        <v>914</v>
+      </c>
       <c r="LW217" t="s">
-        <v>22</v>
+        <v>915</v>
       </c>
       <c r="LX217" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY217" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ217" t="s">
-        <v>914</v>
+        <v>25</v>
       </c>
       <c r="MA217" t="s">
-        <v>915</v>
+        <v>932</v>
       </c>
       <c r="MB217" t="s">
-        <v>932</v>
+        <v>738</v>
       </c>
       <c r="MC217" t="s">
         <v>28</v>
@@ -12801,23 +12801,23 @@
       <c r="LT218" t="s">
         <v>935</v>
       </c>
+      <c r="LU218" t="s">
+        <v>914</v>
+      </c>
       <c r="LW218" t="s">
-        <v>22</v>
+        <v>915</v>
       </c>
       <c r="LX218" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY218" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ218" t="s">
-        <v>914</v>
+        <v>25</v>
       </c>
       <c r="MA218" t="s">
-        <v>915</v>
+        <v>936</v>
       </c>
       <c r="MB218" t="s">
-        <v>936</v>
+        <v>738</v>
       </c>
       <c r="MC218" t="s">
         <v>28</v>
@@ -12836,23 +12836,23 @@
       <c r="LT219" t="s">
         <v>939</v>
       </c>
+      <c r="LU219" t="s">
+        <v>914</v>
+      </c>
       <c r="LW219" t="s">
-        <v>22</v>
+        <v>915</v>
       </c>
       <c r="LX219" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY219" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ219" t="s">
-        <v>914</v>
+        <v>25</v>
       </c>
       <c r="MA219" t="s">
-        <v>915</v>
+        <v>940</v>
       </c>
       <c r="MB219" t="s">
-        <v>940</v>
+        <v>738</v>
       </c>
       <c r="MC219" t="s">
         <v>28</v>
@@ -12871,23 +12871,23 @@
       <c r="LT220" t="s">
         <v>943</v>
       </c>
+      <c r="LU220" t="s">
+        <v>914</v>
+      </c>
       <c r="LW220" t="s">
-        <v>22</v>
+        <v>915</v>
       </c>
       <c r="LX220" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY220" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ220" t="s">
-        <v>914</v>
+        <v>25</v>
       </c>
       <c r="MA220" t="s">
-        <v>915</v>
+        <v>944</v>
       </c>
       <c r="MB220" t="s">
-        <v>944</v>
+        <v>738</v>
       </c>
       <c r="MC220" t="s">
         <v>28</v>
@@ -12906,23 +12906,23 @@
       <c r="LT221" t="s">
         <v>947</v>
       </c>
+      <c r="LU221" t="s">
+        <v>914</v>
+      </c>
       <c r="LW221" t="s">
-        <v>22</v>
+        <v>915</v>
       </c>
       <c r="LX221" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="LY221" t="s">
-        <v>735</v>
-      </c>
-      <c r="LZ221" t="s">
-        <v>914</v>
+        <v>25</v>
       </c>
       <c r="MA221" t="s">
-        <v>915</v>
+        <v>948</v>
       </c>
       <c r="MB221" t="s">
-        <v>948</v>
+        <v>738</v>
       </c>
       <c r="MC221" t="s">
         <v>28</v>
@@ -12941,17 +12941,17 @@
       <c r="LT222" t="s">
         <v>951</v>
       </c>
+      <c r="LU222" t="s">
+        <v>952</v>
+      </c>
       <c r="LW222" t="s">
-        <v>22</v>
+        <v>953</v>
       </c>
       <c r="LX222" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="LY222" t="s">
-        <v>953</v>
-      </c>
-      <c r="LZ222" t="s">
-        <v>954</v>
+        <v>25</v>
       </c>
       <c r="MA222" t="s">
         <v>955</v>
@@ -12976,23 +12976,23 @@
       <c r="LT223" t="s">
         <v>959</v>
       </c>
+      <c r="LU223" t="s">
+        <v>952</v>
+      </c>
       <c r="LW223" t="s">
-        <v>22</v>
+        <v>953</v>
       </c>
       <c r="LX223" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="LY223" t="s">
-        <v>953</v>
-      </c>
-      <c r="LZ223" t="s">
-        <v>954</v>
+        <v>25</v>
       </c>
       <c r="MA223" t="s">
-        <v>955</v>
+        <v>960</v>
       </c>
       <c r="MB223" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="MC223" t="s">
         <v>28</v>
@@ -13011,23 +13011,23 @@
       <c r="LT224" t="s">
         <v>963</v>
       </c>
+      <c r="LU224" t="s">
+        <v>952</v>
+      </c>
       <c r="LW224" t="s">
-        <v>22</v>
+        <v>953</v>
       </c>
       <c r="LX224" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="LY224" t="s">
-        <v>953</v>
-      </c>
-      <c r="LZ224" t="s">
-        <v>954</v>
+        <v>25</v>
       </c>
       <c r="MA224" t="s">
-        <v>955</v>
+        <v>964</v>
       </c>
       <c r="MB224" t="s">
-        <v>964</v>
+        <v>956</v>
       </c>
       <c r="MC224" t="s">
         <v>28</v>
@@ -13046,23 +13046,23 @@
       <c r="LT225" t="s">
         <v>967</v>
       </c>
+      <c r="LU225" t="s">
+        <v>952</v>
+      </c>
       <c r="LW225" t="s">
-        <v>22</v>
+        <v>953</v>
       </c>
       <c r="LX225" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="LY225" t="s">
-        <v>953</v>
-      </c>
-      <c r="LZ225" t="s">
-        <v>954</v>
+        <v>25</v>
       </c>
       <c r="MA225" t="s">
-        <v>955</v>
+        <v>968</v>
       </c>
       <c r="MB225" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="MC225" t="s">
         <v>28</v>
@@ -13081,23 +13081,23 @@
       <c r="LT226" t="s">
         <v>971</v>
       </c>
+      <c r="LU226" t="s">
+        <v>952</v>
+      </c>
       <c r="LW226" t="s">
-        <v>22</v>
+        <v>953</v>
       </c>
       <c r="LX226" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="LY226" t="s">
-        <v>953</v>
-      </c>
-      <c r="LZ226" t="s">
-        <v>954</v>
+        <v>25</v>
       </c>
       <c r="MA226" t="s">
-        <v>955</v>
+        <v>972</v>
       </c>
       <c r="MB226" t="s">
-        <v>972</v>
+        <v>956</v>
       </c>
       <c r="MC226" t="s">
         <v>28</v>
@@ -13116,23 +13116,23 @@
       <c r="LT227" t="s">
         <v>975</v>
       </c>
+      <c r="LU227" t="s">
+        <v>952</v>
+      </c>
       <c r="LW227" t="s">
-        <v>22</v>
+        <v>953</v>
       </c>
       <c r="LX227" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="LY227" t="s">
-        <v>953</v>
-      </c>
-      <c r="LZ227" t="s">
-        <v>954</v>
+        <v>25</v>
       </c>
       <c r="MA227" t="s">
-        <v>955</v>
+        <v>976</v>
       </c>
       <c r="MB227" t="s">
-        <v>976</v>
+        <v>956</v>
       </c>
       <c r="MC227" t="s">
         <v>28</v>
@@ -13151,23 +13151,23 @@
       <c r="LT228" t="s">
         <v>979</v>
       </c>
+      <c r="LU228" t="s">
+        <v>980</v>
+      </c>
       <c r="LW228" t="s">
-        <v>22</v>
+        <v>981</v>
       </c>
       <c r="LX228" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="LY228" t="s">
-        <v>953</v>
-      </c>
-      <c r="LZ228" t="s">
-        <v>980</v>
+        <v>25</v>
       </c>
       <c r="MA228" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="MB228" t="s">
-        <v>982</v>
+        <v>956</v>
       </c>
       <c r="MC228" t="s">
         <v>28</v>
@@ -13186,23 +13186,23 @@
       <c r="LT229" t="s">
         <v>985</v>
       </c>
+      <c r="LU229" t="s">
+        <v>980</v>
+      </c>
       <c r="LW229" t="s">
-        <v>22</v>
+        <v>981</v>
       </c>
       <c r="LX229" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="LY229" t="s">
-        <v>953</v>
-      </c>
-      <c r="LZ229" t="s">
-        <v>980</v>
+        <v>25</v>
       </c>
       <c r="MA229" t="s">
-        <v>981</v>
+        <v>986</v>
       </c>
       <c r="MB229" t="s">
-        <v>986</v>
+        <v>956</v>
       </c>
       <c r="MC229" t="s">
         <v>28</v>
@@ -13221,23 +13221,23 @@
       <c r="LT230" t="s">
         <v>989</v>
       </c>
+      <c r="LU230" t="s">
+        <v>980</v>
+      </c>
       <c r="LW230" t="s">
-        <v>22</v>
+        <v>981</v>
       </c>
       <c r="LX230" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="LY230" t="s">
-        <v>953</v>
-      </c>
-      <c r="LZ230" t="s">
-        <v>980</v>
+        <v>25</v>
       </c>
       <c r="MA230" t="s">
-        <v>981</v>
+        <v>990</v>
       </c>
       <c r="MB230" t="s">
-        <v>990</v>
+        <v>956</v>
       </c>
       <c r="MC230" t="s">
         <v>28</v>
@@ -13256,23 +13256,23 @@
       <c r="LT231" t="s">
         <v>993</v>
       </c>
+      <c r="LU231" t="s">
+        <v>980</v>
+      </c>
       <c r="LW231" t="s">
-        <v>22</v>
+        <v>981</v>
       </c>
       <c r="LX231" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="LY231" t="s">
-        <v>953</v>
-      </c>
-      <c r="LZ231" t="s">
-        <v>980</v>
+        <v>25</v>
       </c>
       <c r="MA231" t="s">
-        <v>981</v>
+        <v>994</v>
       </c>
       <c r="MB231" t="s">
-        <v>994</v>
+        <v>956</v>
       </c>
       <c r="MC231" t="s">
         <v>28</v>
@@ -13291,23 +13291,23 @@
       <c r="LT232" t="s">
         <v>997</v>
       </c>
+      <c r="LU232" t="s">
+        <v>980</v>
+      </c>
       <c r="LW232" t="s">
-        <v>22</v>
+        <v>981</v>
       </c>
       <c r="LX232" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="LY232" t="s">
-        <v>953</v>
-      </c>
-      <c r="LZ232" t="s">
-        <v>980</v>
+        <v>25</v>
       </c>
       <c r="MA232" t="s">
-        <v>981</v>
+        <v>998</v>
       </c>
       <c r="MB232" t="s">
-        <v>998</v>
+        <v>956</v>
       </c>
       <c r="MC232" t="s">
         <v>28</v>
@@ -13326,23 +13326,23 @@
       <c r="LT233" t="s">
         <v>1001</v>
       </c>
+      <c r="LU233" t="s">
+        <v>1002</v>
+      </c>
       <c r="LW233" t="s">
-        <v>22</v>
+        <v>1003</v>
       </c>
       <c r="LX233" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="LY233" t="s">
-        <v>953</v>
-      </c>
-      <c r="LZ233" t="s">
-        <v>1002</v>
+        <v>25</v>
       </c>
       <c r="MA233" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="MB233" t="s">
-        <v>1004</v>
+        <v>956</v>
       </c>
       <c r="MC233" t="s">
         <v>28</v>
@@ -13361,23 +13361,23 @@
       <c r="LT234" t="s">
         <v>1007</v>
       </c>
+      <c r="LU234" t="s">
+        <v>1002</v>
+      </c>
       <c r="LW234" t="s">
-        <v>22</v>
+        <v>1003</v>
       </c>
       <c r="LX234" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="LY234" t="s">
-        <v>953</v>
-      </c>
-      <c r="LZ234" t="s">
-        <v>1002</v>
+        <v>25</v>
       </c>
       <c r="MA234" t="s">
-        <v>1003</v>
+        <v>1008</v>
       </c>
       <c r="MB234" t="s">
-        <v>1008</v>
+        <v>956</v>
       </c>
       <c r="MC234" t="s">
         <v>28</v>
@@ -13396,23 +13396,23 @@
       <c r="LT235" t="s">
         <v>1011</v>
       </c>
+      <c r="LU235" t="s">
+        <v>1002</v>
+      </c>
       <c r="LW235" t="s">
-        <v>22</v>
+        <v>1003</v>
       </c>
       <c r="LX235" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="LY235" t="s">
-        <v>953</v>
-      </c>
-      <c r="LZ235" t="s">
-        <v>1002</v>
+        <v>25</v>
       </c>
       <c r="MA235" t="s">
-        <v>1003</v>
+        <v>1012</v>
       </c>
       <c r="MB235" t="s">
-        <v>1012</v>
+        <v>956</v>
       </c>
       <c r="MC235" t="s">
         <v>28</v>
@@ -13431,23 +13431,23 @@
       <c r="LT236" t="s">
         <v>1015</v>
       </c>
+      <c r="LU236" t="s">
+        <v>1002</v>
+      </c>
       <c r="LW236" t="s">
-        <v>22</v>
+        <v>1003</v>
       </c>
       <c r="LX236" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="LY236" t="s">
-        <v>953</v>
-      </c>
-      <c r="LZ236" t="s">
-        <v>1002</v>
+        <v>25</v>
       </c>
       <c r="MA236" t="s">
-        <v>1003</v>
+        <v>1016</v>
       </c>
       <c r="MB236" t="s">
-        <v>1016</v>
+        <v>956</v>
       </c>
       <c r="MC236" t="s">
         <v>28</v>
@@ -13466,23 +13466,23 @@
       <c r="LT237" t="s">
         <v>1019</v>
       </c>
+      <c r="LU237" t="s">
+        <v>1002</v>
+      </c>
       <c r="LW237" t="s">
-        <v>22</v>
+        <v>1003</v>
       </c>
       <c r="LX237" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="LY237" t="s">
-        <v>953</v>
-      </c>
-      <c r="LZ237" t="s">
-        <v>1002</v>
+        <v>25</v>
       </c>
       <c r="MA237" t="s">
-        <v>1003</v>
+        <v>1020</v>
       </c>
       <c r="MB237" t="s">
-        <v>1020</v>
+        <v>956</v>
       </c>
       <c r="MC237" t="s">
         <v>28</v>
@@ -13501,23 +13501,23 @@
       <c r="LT238" t="s">
         <v>1023</v>
       </c>
+      <c r="LU238" t="s">
+        <v>1002</v>
+      </c>
       <c r="LW238" t="s">
-        <v>22</v>
+        <v>1003</v>
       </c>
       <c r="LX238" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="LY238" t="s">
-        <v>953</v>
-      </c>
-      <c r="LZ238" t="s">
-        <v>1002</v>
+        <v>25</v>
       </c>
       <c r="MA238" t="s">
-        <v>1003</v>
+        <v>1024</v>
       </c>
       <c r="MB238" t="s">
-        <v>1024</v>
+        <v>956</v>
       </c>
       <c r="MC238" t="s">
         <v>28</v>
@@ -13536,23 +13536,23 @@
       <c r="LT239" t="s">
         <v>1027</v>
       </c>
+      <c r="LU239" t="s">
+        <v>1002</v>
+      </c>
       <c r="LW239" t="s">
-        <v>22</v>
+        <v>1003</v>
       </c>
       <c r="LX239" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="LY239" t="s">
-        <v>953</v>
-      </c>
-      <c r="LZ239" t="s">
-        <v>1002</v>
+        <v>25</v>
       </c>
       <c r="MA239" t="s">
-        <v>1003</v>
+        <v>1028</v>
       </c>
       <c r="MB239" t="s">
-        <v>1028</v>
+        <v>956</v>
       </c>
       <c r="MC239" t="s">
         <v>28</v>
@@ -13571,23 +13571,23 @@
       <c r="LT240" t="s">
         <v>1031</v>
       </c>
+      <c r="LU240" t="s">
+        <v>1002</v>
+      </c>
       <c r="LW240" t="s">
-        <v>22</v>
+        <v>1003</v>
       </c>
       <c r="LX240" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="LY240" t="s">
-        <v>953</v>
-      </c>
-      <c r="LZ240" t="s">
-        <v>1002</v>
+        <v>25</v>
       </c>
       <c r="MA240" t="s">
-        <v>1003</v>
+        <v>1032</v>
       </c>
       <c r="MB240" t="s">
-        <v>1032</v>
+        <v>956</v>
       </c>
       <c r="MC240" t="s">
         <v>28</v>
@@ -13606,23 +13606,23 @@
       <c r="LT241" t="s">
         <v>1035</v>
       </c>
+      <c r="LU241" t="s">
+        <v>1036</v>
+      </c>
       <c r="LW241" t="s">
-        <v>22</v>
+        <v>1037</v>
       </c>
       <c r="LX241" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="LY241" t="s">
-        <v>953</v>
-      </c>
-      <c r="LZ241" t="s">
-        <v>1036</v>
+        <v>25</v>
       </c>
       <c r="MA241" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="MB241" t="s">
-        <v>1038</v>
+        <v>956</v>
       </c>
       <c r="MC241" t="s">
         <v>28</v>
@@ -13641,23 +13641,23 @@
       <c r="LT242" t="s">
         <v>1041</v>
       </c>
+      <c r="LU242" t="s">
+        <v>1036</v>
+      </c>
       <c r="LW242" t="s">
-        <v>22</v>
+        <v>1037</v>
       </c>
       <c r="LX242" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="LY242" t="s">
-        <v>953</v>
-      </c>
-      <c r="LZ242" t="s">
-        <v>1036</v>
+        <v>25</v>
       </c>
       <c r="MA242" t="s">
-        <v>1037</v>
+        <v>1042</v>
       </c>
       <c r="MB242" t="s">
-        <v>1042</v>
+        <v>956</v>
       </c>
       <c r="MC242" t="s">
         <v>28</v>
@@ -13676,23 +13676,23 @@
       <c r="LT243" t="s">
         <v>1045</v>
       </c>
+      <c r="LU243" t="s">
+        <v>1036</v>
+      </c>
       <c r="LW243" t="s">
-        <v>22</v>
+        <v>1037</v>
       </c>
       <c r="LX243" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="LY243" t="s">
-        <v>953</v>
-      </c>
-      <c r="LZ243" t="s">
-        <v>1036</v>
+        <v>25</v>
       </c>
       <c r="MA243" t="s">
-        <v>1037</v>
+        <v>1046</v>
       </c>
       <c r="MB243" t="s">
-        <v>1046</v>
+        <v>956</v>
       </c>
       <c r="MC243" t="s">
         <v>28</v>
@@ -13711,23 +13711,23 @@
       <c r="LT244" t="s">
         <v>1049</v>
       </c>
+      <c r="LU244" t="s">
+        <v>1036</v>
+      </c>
       <c r="LW244" t="s">
-        <v>22</v>
+        <v>1037</v>
       </c>
       <c r="LX244" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="LY244" t="s">
-        <v>953</v>
-      </c>
-      <c r="LZ244" t="s">
-        <v>1036</v>
+        <v>25</v>
       </c>
       <c r="MA244" t="s">
-        <v>1037</v>
+        <v>1050</v>
       </c>
       <c r="MB244" t="s">
-        <v>1050</v>
+        <v>956</v>
       </c>
       <c r="MC244" t="s">
         <v>28</v>
@@ -13746,23 +13746,23 @@
       <c r="LT245" t="s">
         <v>1053</v>
       </c>
+      <c r="LU245" t="s">
+        <v>1036</v>
+      </c>
       <c r="LW245" t="s">
-        <v>22</v>
+        <v>1037</v>
       </c>
       <c r="LX245" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="LY245" t="s">
-        <v>953</v>
-      </c>
-      <c r="LZ245" t="s">
-        <v>1036</v>
+        <v>25</v>
       </c>
       <c r="MA245" t="s">
-        <v>1037</v>
+        <v>1054</v>
       </c>
       <c r="MB245" t="s">
-        <v>1054</v>
+        <v>956</v>
       </c>
       <c r="MC245" t="s">
         <v>28</v>
@@ -13781,23 +13781,23 @@
       <c r="LT246" t="s">
         <v>1057</v>
       </c>
+      <c r="LU246" t="s">
+        <v>1036</v>
+      </c>
       <c r="LW246" t="s">
-        <v>22</v>
+        <v>1037</v>
       </c>
       <c r="LX246" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="LY246" t="s">
-        <v>953</v>
-      </c>
-      <c r="LZ246" t="s">
-        <v>1036</v>
+        <v>25</v>
       </c>
       <c r="MA246" t="s">
-        <v>1037</v>
+        <v>1058</v>
       </c>
       <c r="MB246" t="s">
-        <v>1058</v>
+        <v>956</v>
       </c>
       <c r="MC246" t="s">
         <v>28</v>
@@ -13816,23 +13816,23 @@
       <c r="LT247" t="s">
         <v>1061</v>
       </c>
+      <c r="LU247" t="s">
+        <v>1036</v>
+      </c>
       <c r="LW247" t="s">
-        <v>22</v>
+        <v>1037</v>
       </c>
       <c r="LX247" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="LY247" t="s">
-        <v>953</v>
-      </c>
-      <c r="LZ247" t="s">
-        <v>1036</v>
+        <v>25</v>
       </c>
       <c r="MA247" t="s">
-        <v>1037</v>
+        <v>1062</v>
       </c>
       <c r="MB247" t="s">
-        <v>1062</v>
+        <v>956</v>
       </c>
       <c r="MC247" t="s">
         <v>28</v>
@@ -13851,23 +13851,23 @@
       <c r="LT248" t="s">
         <v>1065</v>
       </c>
+      <c r="LU248" t="s">
+        <v>1036</v>
+      </c>
       <c r="LW248" t="s">
-        <v>22</v>
+        <v>1037</v>
       </c>
       <c r="LX248" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="LY248" t="s">
-        <v>953</v>
-      </c>
-      <c r="LZ248" t="s">
-        <v>1036</v>
+        <v>25</v>
       </c>
       <c r="MA248" t="s">
-        <v>1037</v>
+        <v>1066</v>
       </c>
       <c r="MB248" t="s">
-        <v>1066</v>
+        <v>956</v>
       </c>
       <c r="MC248" t="s">
         <v>28</v>
@@ -13886,23 +13886,23 @@
       <c r="LT249" t="s">
         <v>1069</v>
       </c>
+      <c r="LU249" t="s">
+        <v>1036</v>
+      </c>
       <c r="LW249" t="s">
-        <v>22</v>
+        <v>1037</v>
       </c>
       <c r="LX249" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="LY249" t="s">
-        <v>953</v>
-      </c>
-      <c r="LZ249" t="s">
-        <v>1036</v>
+        <v>25</v>
       </c>
       <c r="MA249" t="s">
-        <v>1037</v>
+        <v>1070</v>
       </c>
       <c r="MB249" t="s">
-        <v>1070</v>
+        <v>956</v>
       </c>
       <c r="MC249" t="s">
         <v>28</v>
@@ -13921,23 +13921,23 @@
       <c r="LT250" t="s">
         <v>1073</v>
       </c>
+      <c r="LU250" t="s">
+        <v>1036</v>
+      </c>
       <c r="LW250" t="s">
-        <v>22</v>
+        <v>1037</v>
       </c>
       <c r="LX250" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="LY250" t="s">
-        <v>953</v>
-      </c>
-      <c r="LZ250" t="s">
-        <v>1036</v>
+        <v>25</v>
       </c>
       <c r="MA250" t="s">
-        <v>1037</v>
+        <v>1074</v>
       </c>
       <c r="MB250" t="s">
-        <v>1074</v>
+        <v>956</v>
       </c>
       <c r="MC250" t="s">
         <v>28</v>
